--- a/Sensitivity/Harmonization_SAF/Harmonization Sheets/Moretti_2023_Harmonization.xlsx
+++ b/Sensitivity/Harmonization_SAF/Harmonization Sheets/Moretti_2023_Harmonization.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="94" documentId="13_ncr:1_{AD1138F4-22D8-874F-A515-8FAECA50D6A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C3B01BC-B1DB-40B4-9ADF-70F5F5A1DC85}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="28800" windowHeight="15345" tabRatio="1000" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="28800" windowHeight="15345" tabRatio="1000" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Readme" sheetId="1" r:id="rId1"/>
@@ -836,7 +836,7 @@
         </row>
         <row r="19">
           <cell r="C19">
-            <v>0.8</v>
+            <v>1.7</v>
           </cell>
         </row>
         <row r="21">
@@ -881,12 +881,12 @@
         </row>
         <row r="33">
           <cell r="C33">
-            <v>1282</v>
+            <v>1371</v>
           </cell>
         </row>
         <row r="34">
           <cell r="C34">
-            <v>480</v>
+            <v>523</v>
           </cell>
         </row>
       </sheetData>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="C18" s="4">
         <f>[1]Inputs!C19</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="D18" t="s">
         <v>21</v>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="C32" s="4">
         <f>[1]Inputs!C33</f>
-        <v>1282</v>
+        <v>1371</v>
       </c>
       <c r="D32" t="s">
         <v>29</v>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="C33" s="4">
         <f>[1]Inputs!C34</f>
-        <v>480</v>
+        <v>523</v>
       </c>
       <c r="D33" t="s">
         <v>29</v>
@@ -3496,7 +3496,7 @@
       </c>
       <c r="B36" s="15">
         <f>(Inputs!C32*'Study Parameters'!C17* 1000) / 10^6</f>
-        <v>79.355800000000002</v>
+        <v>84.864900000000006</v>
       </c>
       <c r="C36" s="12" t="s">
         <v>75</v>
@@ -3508,7 +3508,7 @@
       </c>
       <c r="H36" s="15">
         <f>(Inputs!$C$33 * 'Study Parameters'!$C$18 * 1000) / 10 ^ 6</f>
-        <v>56.112000000000002</v>
+        <v>61.138700000000007</v>
       </c>
       <c r="I36" s="12" t="s">
         <v>75</v>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="N36" s="15">
         <f>(Inputs!$C$33 * 'Study Parameters'!$C$18 * 1000) / 10 ^ 6</f>
-        <v>56.112000000000002</v>
+        <v>61.138700000000007</v>
       </c>
       <c r="O36" s="12" t="s">
         <v>75</v>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="B37" s="18">
         <f>B35-B28+B36</f>
-        <v>88.789725937270006</v>
+        <v>94.29882593727001</v>
       </c>
       <c r="C37" s="17" t="s">
         <v>75</v>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="H37" s="18">
         <f>H35-H28+H36</f>
-        <v>69.725991399539566</v>
+        <v>74.752691399539572</v>
       </c>
       <c r="I37" s="17" t="s">
         <v>75</v>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="N37" s="18">
         <f>N35-N28+N36</f>
-        <v>67.585341399539573</v>
+        <v>72.612041399539578</v>
       </c>
       <c r="O37" s="17" t="s">
         <v>75</v>
@@ -6947,103 +6947,103 @@
       </c>
       <c r="C3" s="11">
         <f>'Cost Components'!$B$37*10^6</f>
-        <v>88789725.937270001</v>
+        <v>94298825.937270015</v>
       </c>
       <c r="D3" s="11">
         <f>'Cost Components'!$B$37*10^6</f>
-        <v>88789725.937270001</v>
+        <v>94298825.937270015</v>
       </c>
       <c r="E3" s="11">
         <f>'Cost Components'!$B$37*10^6</f>
-        <v>88789725.937270001</v>
+        <v>94298825.937270015</v>
       </c>
       <c r="F3" s="11">
         <f>'Cost Components'!$B$37*10^6</f>
-        <v>88789725.937270001</v>
+        <v>94298825.937270015</v>
       </c>
       <c r="G3" s="11">
         <f>'Cost Components'!$B$37*10^6</f>
-        <v>88789725.937270001</v>
+        <v>94298825.937270015</v>
       </c>
       <c r="H3" s="11">
         <f>'Cost Components'!$B$37*10^6</f>
-        <v>88789725.937270001</v>
+        <v>94298825.937270015</v>
       </c>
       <c r="I3" s="11">
         <f>'Cost Components'!$B$37*10^6</f>
-        <v>88789725.937270001</v>
+        <v>94298825.937270015</v>
       </c>
       <c r="J3" s="11">
         <f>'Cost Components'!$B$37*10^6</f>
-        <v>88789725.937270001</v>
+        <v>94298825.937270015</v>
       </c>
       <c r="K3" s="11">
         <f>'Cost Components'!$B$37*10^6</f>
-        <v>88789725.937270001</v>
+        <v>94298825.937270015</v>
       </c>
       <c r="L3" s="11">
         <f>'Cost Components'!$B$37*10^6</f>
-        <v>88789725.937270001</v>
+        <v>94298825.937270015</v>
       </c>
       <c r="M3" s="11">
         <f>'Cost Components'!$B$37*10^6</f>
-        <v>88789725.937270001</v>
+        <v>94298825.937270015</v>
       </c>
       <c r="N3" s="11">
         <f>'Cost Components'!$B$37*10^6</f>
-        <v>88789725.937270001</v>
+        <v>94298825.937270015</v>
       </c>
       <c r="O3" s="11">
         <f>'Cost Components'!$B$37*10^6</f>
-        <v>88789725.937270001</v>
+        <v>94298825.937270015</v>
       </c>
       <c r="P3" s="11">
         <f>'Cost Components'!$B$37*10^6</f>
-        <v>88789725.937270001</v>
+        <v>94298825.937270015</v>
       </c>
       <c r="Q3" s="11">
         <f>'Cost Components'!$B$37*10^6</f>
-        <v>88789725.937270001</v>
+        <v>94298825.937270015</v>
       </c>
       <c r="R3" s="11">
         <f>'Cost Components'!$B$37*10^6</f>
-        <v>88789725.937270001</v>
+        <v>94298825.937270015</v>
       </c>
       <c r="S3" s="11">
         <f>'Cost Components'!$B$37*10^6</f>
-        <v>88789725.937270001</v>
+        <v>94298825.937270015</v>
       </c>
       <c r="T3" s="11">
         <f>'Cost Components'!$B$37*10^6</f>
-        <v>88789725.937270001</v>
+        <v>94298825.937270015</v>
       </c>
       <c r="U3" s="11">
         <f>'Cost Components'!$B$37*10^6</f>
-        <v>88789725.937270001</v>
+        <v>94298825.937270015</v>
       </c>
       <c r="V3" s="11">
         <f>'Cost Components'!$B$37*10^6</f>
-        <v>88789725.937270001</v>
+        <v>94298825.937270015</v>
       </c>
       <c r="W3" s="11">
         <f>'Cost Components'!$B$37*10^6</f>
-        <v>88789725.937270001</v>
+        <v>94298825.937270015</v>
       </c>
       <c r="X3" s="11">
         <f>'Cost Components'!$B$37*10^6</f>
-        <v>88789725.937270001</v>
+        <v>94298825.937270015</v>
       </c>
       <c r="Y3" s="11">
         <f>'Cost Components'!$B$37*10^6</f>
-        <v>88789725.937270001</v>
+        <v>94298825.937270015</v>
       </c>
       <c r="Z3" s="11">
         <f>'Cost Components'!$B$37*10^6</f>
-        <v>88789725.937270001</v>
+        <v>94298825.937270015</v>
       </c>
       <c r="AA3" s="11">
         <f>'Cost Components'!$B$37*10^6</f>
-        <v>88789725.937270001</v>
+        <v>94298825.937270015</v>
       </c>
     </row>
     <row r="4" spans="1:27">
@@ -7056,103 +7056,103 @@
       </c>
       <c r="C4" s="8">
         <f>C3 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!C2</f>
-        <v>84374145.648340195</v>
+        <v>89609273.934688002</v>
       </c>
       <c r="D4" s="8">
         <f>D3 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!D2</f>
-        <v>80178155.509984344</v>
+        <v>85152936.90340957</v>
       </c>
       <c r="E4" s="8">
         <f>E3 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!E2</f>
-        <v>76190835.137774169</v>
+        <v>80918216.88635689</v>
       </c>
       <c r="F4" s="8">
         <f>F3 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!F2</f>
-        <v>72401807.22626622</v>
+        <v>76894092.701637834</v>
       </c>
       <c r="G4" s="8">
         <f>G3 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!G2</f>
-        <v>68801210.541272938</v>
+        <v>73070091.259079352</v>
       </c>
       <c r="H4" s="8">
         <f>H3 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!H2</f>
-        <v>65379674.255248271</v>
+        <v>69436260.303211287</v>
       </c>
       <c r="I4" s="8">
         <f>I3 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!I2</f>
-        <v>62128293.558994249</v>
+        <v>65983142.511762396</v>
       </c>
       <c r="J4" s="8">
         <f>J3 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!J2</f>
-        <v>59038606.486215621</v>
+        <v>62701750.882257573</v>
       </c>
       <c r="K4" s="8">
         <f>K3 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!K2</f>
-        <v>56102571.890607178</v>
+        <v>59583545.342658453</v>
       </c>
       <c r="L4" s="8">
         <f>L3 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!L2</f>
-        <v>53312548.518156961</v>
+        <v>56620410.52517432</v>
       </c>
       <c r="M4" s="8">
         <f>M3 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!M2</f>
-        <v>50661275.120199837</v>
+        <v>53804634.645398468</v>
       </c>
       <c r="N4" s="8">
         <f>N3 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!N2</f>
-        <v>48141851.55546388</v>
+        <v>51128889.43180088</v>
       </c>
       <c r="O4" s="8">
         <f>O3 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!O2</f>
-        <v>45747720.831926405</v>
+        <v>48586211.053342618</v>
       </c>
       <c r="P4" s="8">
         <f>P3 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!P2</f>
-        <v>43472652.041741908</v>
+        <v>46169981.995574228</v>
       </c>
       <c r="Q4" s="8">
         <f>Q3 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!Q2</f>
-        <v>41310724.144829184</v>
+        <v>43873913.838049635</v>
       </c>
       <c r="R4" s="8">
         <f>R3 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!R2</f>
-        <v>39256310.558912747</v>
+        <v>41692030.888232149</v>
       </c>
       <c r="S4" s="8">
         <f>S3 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!S2</f>
-        <v>37304064.515913278</v>
+        <v>39618654.629298836</v>
       </c>
       <c r="T4" s="8">
         <f>T3 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!T2</f>
-        <v>35448905.146575809</v>
+        <v>37648388.941367283</v>
       </c>
       <c r="U4" s="8">
         <f>U3 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!U2</f>
-        <v>33686004.257119872</v>
+        <v>35776106.057681933</v>
       </c>
       <c r="V4" s="8">
         <f>V3 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!V2</f>
-        <v>32010773.763496865</v>
+        <v>33996933.219209939</v>
       </c>
       <c r="W4" s="8">
         <f>W3 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!W2</f>
-        <v>30418853.750551343</v>
+        <v>32306239.992914099</v>
       </c>
       <c r="X4" s="8">
         <f>X3 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!X2</f>
-        <v>28906101.125009194</v>
+        <v>30699626.220697589</v>
       </c>
       <c r="Y4" s="8">
         <f>Y3 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!Y2</f>
-        <v>27468578.832761355</v>
+        <v>29172910.567656886</v>
       </c>
       <c r="Z4" s="8">
         <f>Z3 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!Z2</f>
-        <v>26102545.612380121</v>
+        <v>27722119.639838655</v>
       </c>
       <c r="AA4" s="8">
         <f>AA3 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!AA2</f>
-        <v>24804446.258200943</v>
+        <v>26343477.643178958</v>
       </c>
     </row>
     <row r="5" spans="1:27">
@@ -7378,7 +7378,7 @@
       </c>
       <c r="B8" s="8">
         <f>SUM(B4:AA4) / SUM(B6:AA6)</f>
-        <v>3.6717494626837071</v>
+        <v>3.8474512116549016</v>
       </c>
     </row>
     <row r="10" spans="1:27">
@@ -7479,103 +7479,103 @@
       </c>
       <c r="C12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>69725991.39953956</v>
+        <v>74752691.399539575</v>
       </c>
       <c r="D12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>69725991.39953956</v>
+        <v>74752691.399539575</v>
       </c>
       <c r="E12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>69725991.39953956</v>
+        <v>74752691.399539575</v>
       </c>
       <c r="F12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>69725991.39953956</v>
+        <v>74752691.399539575</v>
       </c>
       <c r="G12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>69725991.39953956</v>
+        <v>74752691.399539575</v>
       </c>
       <c r="H12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>69725991.39953956</v>
+        <v>74752691.399539575</v>
       </c>
       <c r="I12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>69725991.39953956</v>
+        <v>74752691.399539575</v>
       </c>
       <c r="J12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>69725991.39953956</v>
+        <v>74752691.399539575</v>
       </c>
       <c r="K12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>69725991.39953956</v>
+        <v>74752691.399539575</v>
       </c>
       <c r="L12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>69725991.39953956</v>
+        <v>74752691.399539575</v>
       </c>
       <c r="M12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>69725991.39953956</v>
+        <v>74752691.399539575</v>
       </c>
       <c r="N12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>69725991.39953956</v>
+        <v>74752691.399539575</v>
       </c>
       <c r="O12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>69725991.39953956</v>
+        <v>74752691.399539575</v>
       </c>
       <c r="P12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>69725991.39953956</v>
+        <v>74752691.399539575</v>
       </c>
       <c r="Q12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>69725991.39953956</v>
+        <v>74752691.399539575</v>
       </c>
       <c r="R12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>69725991.39953956</v>
+        <v>74752691.399539575</v>
       </c>
       <c r="S12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>69725991.39953956</v>
+        <v>74752691.399539575</v>
       </c>
       <c r="T12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>69725991.39953956</v>
+        <v>74752691.399539575</v>
       </c>
       <c r="U12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>69725991.39953956</v>
+        <v>74752691.399539575</v>
       </c>
       <c r="V12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>69725991.39953956</v>
+        <v>74752691.399539575</v>
       </c>
       <c r="W12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>69725991.39953956</v>
+        <v>74752691.399539575</v>
       </c>
       <c r="X12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>69725991.39953956</v>
+        <v>74752691.399539575</v>
       </c>
       <c r="Y12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>69725991.39953956</v>
+        <v>74752691.399539575</v>
       </c>
       <c r="Z12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>69725991.39953956</v>
+        <v>74752691.399539575</v>
       </c>
       <c r="AA12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>69725991.39953956</v>
+        <v>74752691.399539575</v>
       </c>
     </row>
     <row r="13" spans="1:27">
@@ -7588,103 +7588,103 @@
       </c>
       <c r="C13" s="8">
         <f>C12 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!C11</f>
-        <v>66258465.061329961</v>
+        <v>71035183.46487765</v>
       </c>
       <c r="D13" s="8">
         <f>D12 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!D11</f>
-        <v>62963381.433002807</v>
+        <v>67502550.01413776</v>
       </c>
       <c r="E13" s="8">
         <f>E12 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!E11</f>
-        <v>59832164.808048286</v>
+        <v>64145597.099275671</v>
       </c>
       <c r="F13" s="8">
         <f>F12 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!F11</f>
-        <v>56856665.956333488</v>
+        <v>60955587.994243585</v>
       </c>
       <c r="G13" s="8">
         <f>G12 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!G11</f>
-        <v>54029140.915109426</v>
+        <v>57924220.456994221</v>
       </c>
       <c r="H13" s="8">
         <f>H12 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!H11</f>
-        <v>51342230.834757134</v>
+        <v>55043605.122262478</v>
       </c>
       <c r="I13" s="8">
         <f>I12 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!I11</f>
-        <v>48788942.826820217</v>
+        <v>52306244.968890548</v>
       </c>
       <c r="J13" s="8">
         <f>J12 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!J11</f>
-        <v>46362631.764479131</v>
+        <v>49705015.808258347</v>
       </c>
       <c r="K13" s="8">
         <f>K12 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!K11</f>
-        <v>44056982.988101803</v>
+        <v>47233147.743039295</v>
       </c>
       <c r="L13" s="8">
         <f>L12 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!L11</f>
-        <v>41865995.870860122</v>
+        <v>44884207.548025928</v>
       </c>
       <c r="M13" s="8">
         <f>M12 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!M11</f>
-        <v>39783968.201640911</v>
+        <v>42652081.927170672</v>
       </c>
       <c r="N13" s="8">
         <f>N12 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!N11</f>
-        <v>37805481.344606504</v>
+        <v>40530961.603266388</v>
       </c>
       <c r="O13" s="8">
         <f>O12 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!O11</f>
-        <v>35925386.136781596</v>
+        <v>38515326.198859416</v>
       </c>
       <c r="P13" s="8">
         <f>P12 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!P11</f>
-        <v>34138789.486963823</v>
+        <v>36599929.869046003</v>
       </c>
       <c r="Q13" s="8">
         <f>Q12 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!Q11</f>
-        <v>32441041.641080607</v>
+        <v>34779787.648760855</v>
       </c>
       <c r="R13" s="8">
         <f>R12 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!R11</f>
-        <v>30827724.08084948</v>
+        <v>33050162.479025196</v>
       </c>
       <c r="S13" s="8">
         <f>S12 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!S11</f>
-        <v>29294638.024247207</v>
+        <v>31406552.878389478</v>
       </c>
       <c r="T13" s="8">
         <f>T12 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!T11</f>
-        <v>27837793.49785924</v>
+        <v>29844681.227484457</v>
       </c>
       <c r="U13" s="8">
         <f>U12 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!U11</f>
-        <v>26453398.952669535</v>
+        <v>28360482.636190489</v>
       </c>
       <c r="V13" s="8">
         <f>V12 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!V11</f>
-        <v>25137851.396264996</v>
+        <v>26950094.364450887</v>
       </c>
       <c r="W13" s="8">
         <f>W12 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!W11</f>
-        <v>23887727.015772883</v>
+        <v>25609845.769196283</v>
       </c>
       <c r="X13" s="8">
         <f>X12 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!X11</f>
-        <v>22699772.26712659</v>
+        <v>24336248.751215979</v>
       </c>
       <c r="Y13" s="8">
         <f>Y12 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!Y11</f>
-        <v>21570895.407469045</v>
+        <v>23125988.677113701</v>
       </c>
       <c r="Z13" s="8">
         <f>Z12 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!Z11</f>
-        <v>20498158.448656041</v>
+        <v>21975915.75272128</v>
       </c>
       <c r="AA13" s="8">
         <f>AA12 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!AA11</f>
-        <v>19478769.510918003</v>
+        <v>20883036.825519115</v>
       </c>
     </row>
     <row r="14" spans="1:27">
@@ -7910,7 +7910,7 @@
       </c>
       <c r="B17" s="8">
         <f>SUM(B13:AA13) / SUM(B15:AA15)</f>
-        <v>2.977243530357339</v>
+        <v>3.1375600941433475</v>
       </c>
     </row>
     <row r="19" spans="1:27">
@@ -8011,103 +8011,103 @@
       </c>
       <c r="C21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>67585341.399539575</v>
+        <v>72612041.399539575</v>
       </c>
       <c r="D21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>67585341.399539575</v>
+        <v>72612041.399539575</v>
       </c>
       <c r="E21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>67585341.399539575</v>
+        <v>72612041.399539575</v>
       </c>
       <c r="F21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>67585341.399539575</v>
+        <v>72612041.399539575</v>
       </c>
       <c r="G21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>67585341.399539575</v>
+        <v>72612041.399539575</v>
       </c>
       <c r="H21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>67585341.399539575</v>
+        <v>72612041.399539575</v>
       </c>
       <c r="I21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>67585341.399539575</v>
+        <v>72612041.399539575</v>
       </c>
       <c r="J21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>67585341.399539575</v>
+        <v>72612041.399539575</v>
       </c>
       <c r="K21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>67585341.399539575</v>
+        <v>72612041.399539575</v>
       </c>
       <c r="L21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>67585341.399539575</v>
+        <v>72612041.399539575</v>
       </c>
       <c r="M21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>67585341.399539575</v>
+        <v>72612041.399539575</v>
       </c>
       <c r="N21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>67585341.399539575</v>
+        <v>72612041.399539575</v>
       </c>
       <c r="O21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>67585341.399539575</v>
+        <v>72612041.399539575</v>
       </c>
       <c r="P21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>67585341.399539575</v>
+        <v>72612041.399539575</v>
       </c>
       <c r="Q21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>67585341.399539575</v>
+        <v>72612041.399539575</v>
       </c>
       <c r="R21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>67585341.399539575</v>
+        <v>72612041.399539575</v>
       </c>
       <c r="S21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>67585341.399539575</v>
+        <v>72612041.399539575</v>
       </c>
       <c r="T21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>67585341.399539575</v>
+        <v>72612041.399539575</v>
       </c>
       <c r="U21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>67585341.399539575</v>
+        <v>72612041.399539575</v>
       </c>
       <c r="V21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>67585341.399539575</v>
+        <v>72612041.399539575</v>
       </c>
       <c r="W21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>67585341.399539575</v>
+        <v>72612041.399539575</v>
       </c>
       <c r="X21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>67585341.399539575</v>
+        <v>72612041.399539575</v>
       </c>
       <c r="Y21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>67585341.399539575</v>
+        <v>72612041.399539575</v>
       </c>
       <c r="Z21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>67585341.399539575</v>
+        <v>72612041.399539575</v>
       </c>
       <c r="AA21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>67585341.399539575</v>
+        <v>72612041.399539575</v>
       </c>
     </row>
     <row r="22" spans="1:27">
@@ -8120,103 +8120,103 @@
       </c>
       <c r="C22" s="24">
         <f>C21/((1+'Study Parameters'!$C$14) ^'MFSP CO2 Price Corrected'!C20)</f>
-        <v>64147059.035250157</v>
+        <v>68918034.737603992</v>
       </c>
       <c r="D22" s="24">
         <f>D21/((1+'Study Parameters'!$C$14) ^'MFSP CO2 Price Corrected'!D20)</f>
-        <v>60883693.085848674</v>
+        <v>65411954.003040999</v>
       </c>
       <c r="E22" s="24">
         <f>E21/((1+'Study Parameters'!$C$14) ^'MFSP CO2 Price Corrected'!E20)</f>
-        <v>57786344.994161606</v>
+        <v>62084238.803190008</v>
       </c>
       <c r="F22" s="24">
         <f>F21/((1+'Study Parameters'!$C$14) ^'MFSP CO2 Price Corrected'!F20)</f>
-        <v>54846568.901064537</v>
+        <v>58925815.113126427</v>
       </c>
       <c r="G22" s="24">
         <f>G21/((1+'Study Parameters'!$C$14) ^'MFSP CO2 Price Corrected'!G20)</f>
-        <v>52056348.61528524</v>
+        <v>55928070.532580122</v>
       </c>
       <c r="H22" s="24">
         <f>H21/((1+'Study Parameters'!$C$14) ^'MFSP CO2 Price Corrected'!H20)</f>
-        <v>49408075.754826538</v>
+        <v>53082830.801613629</v>
       </c>
       <c r="I22" s="24">
         <f>I21/((1+'Study Parameters'!$C$14) ^'MFSP CO2 Price Corrected'!I20)</f>
-        <v>46894529.000404835</v>
+        <v>50382337.511022806</v>
       </c>
       <c r="J22" s="24">
         <f>J21/((1+'Study Parameters'!$C$14) ^'MFSP CO2 Price Corrected'!J20)</f>
-        <v>44508854.404332608</v>
+        <v>47819226.946680717</v>
       </c>
       <c r="K22" s="24">
         <f>K21/((1+'Study Parameters'!$C$14) ^'MFSP CO2 Price Corrected'!K20)</f>
-        <v>42244546.701150917</v>
+        <v>45386510.010137349</v>
       </c>
       <c r="L22" s="24">
         <f>L21/((1+'Study Parameters'!$C$14) ^'MFSP CO2 Price Corrected'!L20)</f>
-        <v>40095431.569049843</v>
+        <v>43077553.160722613</v>
       </c>
       <c r="M22" s="24">
         <f>M21/((1+'Study Parameters'!$C$14) ^'MFSP CO2 Price Corrected'!M20)</f>
-        <v>38055648.793707132</v>
+        <v>40886060.327185467</v>
       </c>
       <c r="N22" s="24">
         <f>N21/((1+'Study Parameters'!$C$14) ^'MFSP CO2 Price Corrected'!N20)</f>
-        <v>36119636.28863623</v>
+        <v>38806055.739545815</v>
       </c>
       <c r="O22" s="24">
         <f>O21/((1+'Study Parameters'!$C$14) ^'MFSP CO2 Price Corrected'!O20)</f>
-        <v>34282114.928470224</v>
+        <v>36831867.634344921</v>
       </c>
       <c r="P22" s="24">
         <f>P21/((1+'Study Parameters'!$C$14) ^'MFSP CO2 Price Corrected'!P20)</f>
-        <v>32538074.15382519</v>
+        <v>34958112.788861923</v>
       </c>
       <c r="Q22" s="24">
         <f>Q21/((1+'Study Parameters'!$C$14) ^'MFSP CO2 Price Corrected'!Q20)</f>
-        <v>30882758.308490116</v>
+        <v>33179681.842124067</v>
       </c>
       <c r="R22" s="24">
         <f>R21/((1+'Study Parameters'!$C$14) ^'MFSP CO2 Price Corrected'!R20)</f>
-        <v>29311653.671687659</v>
+        <v>31491725.36268419</v>
       </c>
       <c r="S22" s="24">
         <f>S21/((1+'Study Parameters'!$C$14) ^'MFSP CO2 Price Corrected'!S20)</f>
-        <v>27820476.150045227</v>
+        <v>29889640.625174817</v>
       </c>
       <c r="T22" s="24">
         <f>T21/((1+'Study Parameters'!$C$14) ^'MFSP CO2 Price Corrected'!T20)</f>
-        <v>26405159.595714912</v>
+        <v>28369059.059581261</v>
       </c>
       <c r="U22" s="24">
         <f>U21/((1+'Study Parameters'!$C$14) ^'MFSP CO2 Price Corrected'!U20)</f>
-        <v>25061844.718787879</v>
+        <v>26925834.339010309</v>
       </c>
       <c r="V22" s="24">
         <f>V21/((1+'Study Parameters'!$C$14) ^'MFSP CO2 Price Corrected'!V20)</f>
-        <v>23786868.563769814</v>
+        <v>25556031.073472198</v>
       </c>
       <c r="W22" s="24">
         <f>W21/((1+'Study Parameters'!$C$14) ^'MFSP CO2 Price Corrected'!W20)</f>
-        <v>22576754.521421611</v>
+        <v>24255914.078846045</v>
       </c>
       <c r="X22" s="24">
         <f>X21/((1+'Study Parameters'!$C$14) ^'MFSP CO2 Price Corrected'!X20)</f>
-        <v>21428202.8487297</v>
+        <v>23021938.191767313</v>
       </c>
       <c r="Y22" s="24">
         <f>Y21/((1+'Study Parameters'!$C$14) ^'MFSP CO2 Price Corrected'!Y20)</f>
-        <v>20338081.671155751</v>
+        <v>21850738.602664497</v>
       </c>
       <c r="Z22" s="24">
         <f>Z21/((1+'Study Parameters'!$C$14) ^'MFSP CO2 Price Corrected'!Z20)</f>
-        <v>19303418.442630742</v>
+        <v>20739121.680585131</v>
       </c>
       <c r="AA22" s="24">
         <f>AA21/((1+'Study Parameters'!$C$14) ^'MFSP CO2 Price Corrected'!AA20)</f>
-        <v>18321391.840006396</v>
+        <v>19684056.264792267</v>
       </c>
     </row>
     <row r="23" spans="1:27">
@@ -8442,7 +8442,7 @@
       </c>
       <c r="B26" s="8">
         <f>SUM(B22:AA22) / SUM(B24:AA24)</f>
-        <v>2.7613166824414148</v>
+        <v>2.9216332462274224</v>
       </c>
     </row>
   </sheetData>
@@ -8558,103 +8558,103 @@
       </c>
       <c r="C3" s="11">
         <f>'Cost Components'!$B$37*10^6</f>
-        <v>88789725.937270001</v>
+        <v>94298825.937270015</v>
       </c>
       <c r="D3" s="11">
         <f>'Cost Components'!$B$37*10^6</f>
-        <v>88789725.937270001</v>
+        <v>94298825.937270015</v>
       </c>
       <c r="E3" s="11">
         <f>'Cost Components'!$B$37*10^6</f>
-        <v>88789725.937270001</v>
+        <v>94298825.937270015</v>
       </c>
       <c r="F3" s="11">
         <f>'Cost Components'!$B$37*10^6</f>
-        <v>88789725.937270001</v>
+        <v>94298825.937270015</v>
       </c>
       <c r="G3" s="11">
         <f>'Cost Components'!$B$37*10^6</f>
-        <v>88789725.937270001</v>
+        <v>94298825.937270015</v>
       </c>
       <c r="H3" s="11">
         <f>'Cost Components'!$B$37*10^6</f>
-        <v>88789725.937270001</v>
+        <v>94298825.937270015</v>
       </c>
       <c r="I3" s="11">
         <f>'Cost Components'!$B$37*10^6</f>
-        <v>88789725.937270001</v>
+        <v>94298825.937270015</v>
       </c>
       <c r="J3" s="11">
         <f>'Cost Components'!$B$37*10^6</f>
-        <v>88789725.937270001</v>
+        <v>94298825.937270015</v>
       </c>
       <c r="K3" s="11">
         <f>'Cost Components'!$B$37*10^6</f>
-        <v>88789725.937270001</v>
+        <v>94298825.937270015</v>
       </c>
       <c r="L3" s="11">
         <f>'Cost Components'!$B$37*10^6</f>
-        <v>88789725.937270001</v>
+        <v>94298825.937270015</v>
       </c>
       <c r="M3" s="11">
         <f>'Cost Components'!$B$37*10^6</f>
-        <v>88789725.937270001</v>
+        <v>94298825.937270015</v>
       </c>
       <c r="N3" s="11">
         <f>'Cost Components'!$B$37*10^6</f>
-        <v>88789725.937270001</v>
+        <v>94298825.937270015</v>
       </c>
       <c r="O3" s="11">
         <f>'Cost Components'!$B$37*10^6</f>
-        <v>88789725.937270001</v>
+        <v>94298825.937270015</v>
       </c>
       <c r="P3" s="11">
         <f>'Cost Components'!$B$37*10^6</f>
-        <v>88789725.937270001</v>
+        <v>94298825.937270015</v>
       </c>
       <c r="Q3" s="11">
         <f>'Cost Components'!$B$37*10^6</f>
-        <v>88789725.937270001</v>
+        <v>94298825.937270015</v>
       </c>
       <c r="R3" s="11">
         <f>'Cost Components'!$B$37*10^6</f>
-        <v>88789725.937270001</v>
+        <v>94298825.937270015</v>
       </c>
       <c r="S3" s="11">
         <f>'Cost Components'!$B$37*10^6</f>
-        <v>88789725.937270001</v>
+        <v>94298825.937270015</v>
       </c>
       <c r="T3" s="11">
         <f>'Cost Components'!$B$37*10^6</f>
-        <v>88789725.937270001</v>
+        <v>94298825.937270015</v>
       </c>
       <c r="U3" s="11">
         <f>'Cost Components'!$B$37*10^6</f>
-        <v>88789725.937270001</v>
+        <v>94298825.937270015</v>
       </c>
       <c r="V3" s="11">
         <f>'Cost Components'!$B$37*10^6</f>
-        <v>88789725.937270001</v>
+        <v>94298825.937270015</v>
       </c>
       <c r="W3" s="11">
         <f>'Cost Components'!$B$37*10^6</f>
-        <v>88789725.937270001</v>
+        <v>94298825.937270015</v>
       </c>
       <c r="X3" s="11">
         <f>'Cost Components'!$B$37*10^6</f>
-        <v>88789725.937270001</v>
+        <v>94298825.937270015</v>
       </c>
       <c r="Y3" s="11">
         <f>'Cost Components'!$B$37*10^6</f>
-        <v>88789725.937270001</v>
+        <v>94298825.937270015</v>
       </c>
       <c r="Z3" s="11">
         <f>'Cost Components'!$B$37*10^6</f>
-        <v>88789725.937270001</v>
+        <v>94298825.937270015</v>
       </c>
       <c r="AA3" s="11">
         <f>'Cost Components'!$B$37*10^6</f>
-        <v>88789725.937270001</v>
+        <v>94298825.937270015</v>
       </c>
     </row>
     <row r="4" spans="1:27">
@@ -8667,103 +8667,103 @@
       </c>
       <c r="C4" s="8">
         <f>C3 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!C2</f>
-        <v>82981052.27782242</v>
+        <v>88129743.866607487</v>
       </c>
       <c r="D4" s="8">
         <f>D3 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!D2</f>
-        <v>77552385.3063761</v>
+        <v>82364246.604306057</v>
       </c>
       <c r="E4" s="8">
         <f>E3 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!E2</f>
-        <v>72478864.772314116</v>
+        <v>76975931.40589352</v>
       </c>
       <c r="F4" s="8">
         <f>F3 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!F2</f>
-        <v>67737256.796555251</v>
+        <v>71940122.809246287</v>
       </c>
       <c r="G4" s="8">
         <f>G3 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!G2</f>
-        <v>63305847.473416112</v>
+        <v>67233759.634809598</v>
       </c>
       <c r="H4" s="8">
         <f>H3 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!H2</f>
-        <v>59164343.433099173</v>
+        <v>62835289.378326736</v>
       </c>
       <c r="I4" s="8">
         <f>I3 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!I2</f>
-        <v>55293778.909438476</v>
+        <v>58724569.51245489</v>
       </c>
       <c r="J4" s="8">
         <f>J3 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!J2</f>
-        <v>51676428.887325682</v>
+        <v>54882775.245284945</v>
       </c>
       <c r="K4" s="8">
         <f>K3 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!K2</f>
-        <v>48295727.932080068</v>
+        <v>51292313.313350409</v>
       </c>
       <c r="L4" s="8">
         <f>L3 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!L2</f>
-        <v>45136194.329046801</v>
+        <v>47936741.414346181</v>
       </c>
       <c r="M4" s="8">
         <f>M3 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!M2</f>
-        <v>42183359.186025038</v>
+        <v>44800692.910603896</v>
       </c>
       <c r="N4" s="8">
         <f>N3 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!N2</f>
-        <v>39423700.173855186</v>
+        <v>41869806.458508328</v>
       </c>
       <c r="O4" s="8">
         <f>O3 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!O2</f>
-        <v>36844579.601733811</v>
+        <v>39130660.241596565</v>
       </c>
       <c r="P4" s="8">
         <f>P3 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!P2</f>
-        <v>34434186.543676466</v>
+        <v>36570710.506165013</v>
       </c>
       <c r="Q4" s="8">
         <f>Q3 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!Q2</f>
-        <v>32181482.751099493</v>
+        <v>34178234.117911227</v>
       </c>
       <c r="R4" s="8">
         <f>R3 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!R2</f>
-        <v>30076152.103831306</v>
+        <v>31942274.876552548</v>
       </c>
       <c r="S4" s="8">
         <f>S3 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!S2</f>
-        <v>28108553.368066642</v>
+        <v>29852593.342572477</v>
       </c>
       <c r="T4" s="8">
         <f>T3 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!T2</f>
-        <v>26269676.044922095</v>
+        <v>27899619.946329415</v>
       </c>
       <c r="U4" s="8">
         <f>U3 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!U2</f>
-        <v>24551099.107403826</v>
+        <v>26074411.164793845</v>
       </c>
       <c r="V4" s="8">
         <f>V3 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!V2</f>
-        <v>22944952.436826006</v>
+        <v>24368608.565227896</v>
       </c>
       <c r="W4" s="8">
         <f>W3 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!W2</f>
-        <v>21443880.782080378</v>
+        <v>22774400.528250366</v>
       </c>
       <c r="X4" s="8">
         <f>X3 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!X2</f>
-        <v>20041010.076710634</v>
+        <v>21284486.475000344</v>
       </c>
       <c r="Y4" s="8">
         <f>Y3 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!Y2</f>
-        <v>18729915.959542651</v>
+        <v>19892043.43457976</v>
       </c>
       <c r="Z4" s="8">
         <f>Z3 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!Z2</f>
-        <v>17504594.354712754</v>
+        <v>18590694.798672672</v>
       </c>
       <c r="AA4" s="8">
         <f>AA3 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!AA2</f>
-        <v>16359433.97636706</v>
+        <v>17374481.120254833</v>
       </c>
     </row>
     <row r="5" spans="1:27">
@@ -8989,7 +8989,7 @@
       </c>
       <c r="B8" s="8">
         <f>SUM(B4:AA4) / SUM(B6:AA6)</f>
-        <v>3.8243100954201164</v>
+        <v>4.0000118443913113</v>
       </c>
     </row>
     <row r="10" spans="1:27">
@@ -9090,103 +9090,103 @@
       </c>
       <c r="C12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>69725991.39953956</v>
+        <v>74752691.399539575</v>
       </c>
       <c r="D12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>69725991.39953956</v>
+        <v>74752691.399539575</v>
       </c>
       <c r="E12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>69725991.39953956</v>
+        <v>74752691.399539575</v>
       </c>
       <c r="F12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>69725991.39953956</v>
+        <v>74752691.399539575</v>
       </c>
       <c r="G12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>69725991.39953956</v>
+        <v>74752691.399539575</v>
       </c>
       <c r="H12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>69725991.39953956</v>
+        <v>74752691.399539575</v>
       </c>
       <c r="I12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>69725991.39953956</v>
+        <v>74752691.399539575</v>
       </c>
       <c r="J12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>69725991.39953956</v>
+        <v>74752691.399539575</v>
       </c>
       <c r="K12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>69725991.39953956</v>
+        <v>74752691.399539575</v>
       </c>
       <c r="L12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>69725991.39953956</v>
+        <v>74752691.399539575</v>
       </c>
       <c r="M12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>69725991.39953956</v>
+        <v>74752691.399539575</v>
       </c>
       <c r="N12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>69725991.39953956</v>
+        <v>74752691.399539575</v>
       </c>
       <c r="O12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>69725991.39953956</v>
+        <v>74752691.399539575</v>
       </c>
       <c r="P12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>69725991.39953956</v>
+        <v>74752691.399539575</v>
       </c>
       <c r="Q12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>69725991.39953956</v>
+        <v>74752691.399539575</v>
       </c>
       <c r="R12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>69725991.39953956</v>
+        <v>74752691.399539575</v>
       </c>
       <c r="S12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>69725991.39953956</v>
+        <v>74752691.399539575</v>
       </c>
       <c r="T12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>69725991.39953956</v>
+        <v>74752691.399539575</v>
       </c>
       <c r="U12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>69725991.39953956</v>
+        <v>74752691.399539575</v>
       </c>
       <c r="V12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>69725991.39953956</v>
+        <v>74752691.399539575</v>
       </c>
       <c r="W12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>69725991.39953956</v>
+        <v>74752691.399539575</v>
       </c>
       <c r="X12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>69725991.39953956</v>
+        <v>74752691.399539575</v>
       </c>
       <c r="Y12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>69725991.39953956</v>
+        <v>74752691.399539575</v>
       </c>
       <c r="Z12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>69725991.39953956</v>
+        <v>74752691.399539575</v>
       </c>
       <c r="AA12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>69725991.39953956</v>
+        <v>74752691.399539575</v>
       </c>
     </row>
     <row r="13" spans="1:27">
@@ -9199,103 +9199,103 @@
       </c>
       <c r="C13" s="8">
         <f>C12 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!C11</f>
-        <v>65164477.943494909</v>
+        <v>69862328.410784647</v>
       </c>
       <c r="D13" s="8">
         <f>D12 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!D11</f>
-        <v>60901381.255602725</v>
+        <v>65291895.71101369</v>
       </c>
       <c r="E13" s="8">
         <f>E12 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!E11</f>
-        <v>56917178.743553944</v>
+        <v>61020463.281321205</v>
       </c>
       <c r="F13" s="8">
         <f>F12 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!F11</f>
-        <v>53193624.993975654</v>
+        <v>57028470.356374957</v>
       </c>
       <c r="G13" s="8">
         <f>G12 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!G11</f>
-        <v>49713668.218668826</v>
+        <v>53297635.847079396</v>
       </c>
       <c r="H13" s="8">
         <f>H12 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!H11</f>
-        <v>46461372.166980214</v>
+        <v>49810874.623438694</v>
       </c>
       <c r="I13" s="8">
         <f>I12 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!I11</f>
-        <v>43421843.146710478</v>
+        <v>46552219.274241768</v>
       </c>
       <c r="J13" s="8">
         <f>J12 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!J11</f>
-        <v>40581161.819355592</v>
+        <v>43506746.985272676</v>
       </c>
       <c r="K13" s="8">
         <f>K12 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!K11</f>
-        <v>37926319.457341671</v>
+        <v>40660511.201189414</v>
       </c>
       <c r="L13" s="8">
         <f>L12 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!L11</f>
-        <v>35445158.371347353</v>
+        <v>38000477.758120947</v>
       </c>
       <c r="M13" s="8">
         <f>M12 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!M11</f>
-        <v>33126316.234904066</v>
+        <v>35514465.194505557</v>
       </c>
       <c r="N13" s="8">
         <f>N12 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!N11</f>
-        <v>30959174.051312219</v>
+        <v>33191088.966827627</v>
       </c>
       <c r="O13" s="8">
         <f>O12 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!O11</f>
-        <v>28933807.524590857</v>
+        <v>31019709.314792175</v>
       </c>
       <c r="P13" s="8">
         <f>P12 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!P11</f>
-        <v>27040941.611767158</v>
+        <v>28990382.537188951</v>
       </c>
       <c r="Q13" s="8">
         <f>Q12 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!Q11</f>
-        <v>25271908.048380516</v>
+        <v>27093815.455316771</v>
       </c>
       <c r="R13" s="8">
         <f>R12 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!R11</f>
-        <v>23618605.652692076</v>
+        <v>25321322.855436239</v>
       </c>
       <c r="S13" s="8">
         <f>S12 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!S11</f>
-        <v>22073463.226815023</v>
+        <v>23664787.715360969</v>
       </c>
       <c r="T13" s="8">
         <f>T12 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!T11</f>
-        <v>20629404.884873852</v>
+        <v>22116624.033047635</v>
       </c>
       <c r="U13" s="8">
         <f>U12 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!U11</f>
-        <v>19279817.649414815</v>
+        <v>20669742.086960405</v>
       </c>
       <c r="V13" s="8">
         <f>V12 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!V11</f>
-        <v>18018521.167677399</v>
+        <v>19317515.969121877</v>
       </c>
       <c r="W13" s="8">
         <f>W12 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!W11</f>
-        <v>16839739.409044296</v>
+        <v>18053753.242169976</v>
       </c>
       <c r="X13" s="8">
         <f>X12 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!X11</f>
-        <v>15738074.21406009</v>
+        <v>16872666.581467267</v>
       </c>
       <c r="Y13" s="8">
         <f>Y12 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!Y11</f>
-        <v>14708480.573887935</v>
+        <v>15768847.272399316</v>
       </c>
       <c r="Z13" s="8">
         <f>Z12 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!Z11</f>
-        <v>13746243.526998069</v>
+        <v>14737240.441494687</v>
       </c>
       <c r="AA13" s="8">
         <f>AA12 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!AA11</f>
-        <v>12846956.567287914</v>
+        <v>13773121.907938959</v>
       </c>
     </row>
     <row r="14" spans="1:27">
@@ -9521,7 +9521,7 @@
       </c>
       <c r="B17" s="8">
         <f>SUM(B13:AA13) / SUM(B15:AA15)</f>
-        <v>3.1140925254267096</v>
+        <v>3.2744090892127193</v>
       </c>
     </row>
     <row r="19" spans="1:30">
@@ -9622,103 +9622,103 @@
       </c>
       <c r="C21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>67585341.399539575</v>
+        <v>72612041.399539575</v>
       </c>
       <c r="D21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>67585341.399539575</v>
+        <v>72612041.399539575</v>
       </c>
       <c r="E21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>67585341.399539575</v>
+        <v>72612041.399539575</v>
       </c>
       <c r="F21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>67585341.399539575</v>
+        <v>72612041.399539575</v>
       </c>
       <c r="G21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>67585341.399539575</v>
+        <v>72612041.399539575</v>
       </c>
       <c r="H21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>67585341.399539575</v>
+        <v>72612041.399539575</v>
       </c>
       <c r="I21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>67585341.399539575</v>
+        <v>72612041.399539575</v>
       </c>
       <c r="J21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>67585341.399539575</v>
+        <v>72612041.399539575</v>
       </c>
       <c r="K21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>67585341.399539575</v>
+        <v>72612041.399539575</v>
       </c>
       <c r="L21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>67585341.399539575</v>
+        <v>72612041.399539575</v>
       </c>
       <c r="M21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>67585341.399539575</v>
+        <v>72612041.399539575</v>
       </c>
       <c r="N21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>67585341.399539575</v>
+        <v>72612041.399539575</v>
       </c>
       <c r="O21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>67585341.399539575</v>
+        <v>72612041.399539575</v>
       </c>
       <c r="P21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>67585341.399539575</v>
+        <v>72612041.399539575</v>
       </c>
       <c r="Q21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>67585341.399539575</v>
+        <v>72612041.399539575</v>
       </c>
       <c r="R21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>67585341.399539575</v>
+        <v>72612041.399539575</v>
       </c>
       <c r="S21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>67585341.399539575</v>
+        <v>72612041.399539575</v>
       </c>
       <c r="T21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>67585341.399539575</v>
+        <v>72612041.399539575</v>
       </c>
       <c r="U21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>67585341.399539575</v>
+        <v>72612041.399539575</v>
       </c>
       <c r="V21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>67585341.399539575</v>
+        <v>72612041.399539575</v>
       </c>
       <c r="W21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>67585341.399539575</v>
+        <v>72612041.399539575</v>
       </c>
       <c r="X21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>67585341.399539575</v>
+        <v>72612041.399539575</v>
       </c>
       <c r="Y21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>67585341.399539575</v>
+        <v>72612041.399539575</v>
       </c>
       <c r="Z21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>67585341.399539575</v>
+        <v>72612041.399539575</v>
       </c>
       <c r="AA21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>67585341.399539575</v>
+        <v>72612041.399539575</v>
       </c>
     </row>
     <row r="22" spans="1:30">
@@ -9731,103 +9731,103 @@
       </c>
       <c r="C22" s="24">
         <f>C21/((1+Inputs!$C$5) ^ 'MFSP WACC Corrected'!C20)</f>
-        <v>63163870.466859415</v>
+        <v>67861720.934149131</v>
       </c>
       <c r="D22" s="24">
         <f>D21/((1+Inputs!$C$5) ^ 'MFSP WACC Corrected'!D20)</f>
-        <v>59031654.641924687</v>
+        <v>63422169.097335637</v>
       </c>
       <c r="E22" s="24">
         <f>E21/((1+Inputs!$C$5) ^ 'MFSP WACC Corrected'!E20)</f>
-        <v>55169770.693387553</v>
+        <v>59273055.231154799</v>
       </c>
       <c r="F22" s="24">
         <f>F21/((1+Inputs!$C$5) ^ 'MFSP WACC Corrected'!F20)</f>
-        <v>51560533.358306132</v>
+        <v>55395378.720705427</v>
       </c>
       <c r="G22" s="24">
         <f>G21/((1+Inputs!$C$5) ^ 'MFSP WACC Corrected'!G20)</f>
-        <v>48187414.353557125</v>
+        <v>51771381.98196768</v>
       </c>
       <c r="H22" s="24">
         <f>H21/((1+Inputs!$C$5) ^ 'MFSP WACC Corrected'!H20)</f>
-        <v>45034966.685567409</v>
+        <v>48384469.142025873</v>
       </c>
       <c r="I22" s="24">
         <f>I21/((1+Inputs!$C$5) ^ 'MFSP WACC Corrected'!I20)</f>
-        <v>42088753.911745243</v>
+        <v>45219130.03927651</v>
       </c>
       <c r="J22" s="24">
         <f>J21/((1+Inputs!$C$5) ^ 'MFSP WACC Corrected'!J20)</f>
-        <v>39335284.02966845</v>
+        <v>42260869.195585527</v>
       </c>
       <c r="K22" s="24">
         <f>K21/((1+Inputs!$C$5) ^ 'MFSP WACC Corrected'!K20)</f>
-        <v>36761947.69127892</v>
+        <v>39496139.435126655</v>
       </c>
       <c r="L22" s="24">
         <f>L21/((1+Inputs!$C$5) ^ 'MFSP WACC Corrected'!L20)</f>
-        <v>34356960.459139183</v>
+        <v>36912279.845912769</v>
       </c>
       <c r="M22" s="24">
         <f>M21/((1+Inputs!$C$5) ^ 'MFSP WACC Corrected'!M20)</f>
-        <v>32109308.840316985</v>
+        <v>34497457.799918465</v>
       </c>
       <c r="N22" s="24">
         <f>N21/((1+Inputs!$C$5) ^ 'MFSP WACC Corrected'!N20)</f>
-        <v>30008699.850763544</v>
+        <v>32240614.766278949</v>
       </c>
       <c r="O22" s="24">
         <f>O21/((1+Inputs!$C$5) ^ 'MFSP WACC Corrected'!O20)</f>
-        <v>28045513.879218265</v>
+        <v>30131415.669419575</v>
       </c>
       <c r="P22" s="24">
         <f>P21/((1+Inputs!$C$5) ^ 'MFSP WACC Corrected'!P20)</f>
-        <v>26210760.634783424</v>
+        <v>28160201.560205214</v>
       </c>
       <c r="Q22" s="24">
         <f>Q21/((1+Inputs!$C$5) ^ 'MFSP WACC Corrected'!Q20)</f>
-        <v>24496037.976433106</v>
+        <v>26317945.383369353</v>
       </c>
       <c r="R22" s="24">
         <f>R21/((1+Inputs!$C$5) ^ 'MFSP WACC Corrected'!R20)</f>
-        <v>22893493.435918793</v>
+        <v>24596210.638662953</v>
       </c>
       <c r="S22" s="24">
         <f>S21/((1+Inputs!$C$5) ^ 'MFSP WACC Corrected'!S20)</f>
-        <v>21395788.257868029</v>
+        <v>22987112.746413972</v>
       </c>
       <c r="T22" s="24">
         <f>T21/((1+Inputs!$C$5) ^ 'MFSP WACC Corrected'!T20)</f>
-        <v>19996063.792400029</v>
+        <v>21483282.940573808</v>
       </c>
       <c r="U22" s="24">
         <f>U21/((1+Inputs!$C$5) ^ 'MFSP WACC Corrected'!U20)</f>
-        <v>18687910.086355165</v>
+        <v>20077834.523900751</v>
       </c>
       <c r="V22" s="24">
         <f>V21/((1+Inputs!$C$5) ^ 'MFSP WACC Corrected'!V20)</f>
-        <v>17465336.529303893</v>
+        <v>18764331.330748368</v>
       </c>
       <c r="W22" s="24">
         <f>W21/((1+Inputs!$C$5) ^ 'MFSP WACC Corrected'!W20)</f>
-        <v>16322744.419910181</v>
+        <v>17536758.253035858</v>
       </c>
       <c r="X22" s="24">
         <f>X21/((1+Inputs!$C$5) ^ 'MFSP WACC Corrected'!X20)</f>
-        <v>15254901.327018861</v>
+        <v>16389493.694426036</v>
       </c>
       <c r="Y22" s="24">
         <f>Y21/((1+Inputs!$C$5) ^ 'MFSP WACC Corrected'!Y20)</f>
-        <v>14256917.12805501</v>
+        <v>15317283.826566387</v>
       </c>
       <c r="Z22" s="24">
         <f>Z21/((1+Inputs!$C$5) ^ 'MFSP WACC Corrected'!Z20)</f>
-        <v>13324221.615004681</v>
+        <v>14315218.529501297</v>
       </c>
       <c r="AA22" s="24">
         <f>AA21/((1+Inputs!$C$5) ^ 'MFSP WACC Corrected'!AA20)</f>
-        <v>12452543.565424934</v>
+        <v>13378708.906075977</v>
       </c>
     </row>
     <row r="23" spans="1:30">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="B26" s="8">
         <f>SUM(B22:AA22) / SUM(B24:AA24)</f>
-        <v>2.8624581691846087</v>
+        <v>3.0227747329706167</v>
       </c>
     </row>
     <row r="29" spans="1:30">
@@ -10348,103 +10348,103 @@
       </c>
       <c r="C33">
         <f>('Cost Components'!$B$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!C30</f>
-        <v>74164299.065420553</v>
+        <v>79312990.654205605</v>
       </c>
       <c r="D33">
         <f>('Cost Components'!$B$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!D30</f>
-        <v>69312429.033103332</v>
+        <v>74124290.331033275</v>
       </c>
       <c r="E33">
         <f>('Cost Components'!$B$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!E30</f>
-        <v>64777971.058975071</v>
+        <v>69275037.692554459</v>
       </c>
       <c r="F33">
         <f>('Cost Components'!$B$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!F30</f>
-        <v>60540159.868201002</v>
+        <v>64743025.880892023</v>
       </c>
       <c r="G33">
         <f>('Cost Components'!$B$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!G30</f>
-        <v>56579588.661870092</v>
+        <v>60507500.823263563</v>
       </c>
       <c r="H33">
         <f>('Cost Components'!$B$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!H30</f>
-        <v>52878120.244738407</v>
+        <v>56549066.189965956</v>
       </c>
       <c r="I33">
         <f>('Cost Components'!$B$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!I30</f>
-        <v>49418803.967045233</v>
+        <v>52849594.570061639</v>
       </c>
       <c r="J33">
         <f>('Cost Components'!$B$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!J30</f>
-        <v>46185798.100042276</v>
+        <v>49392144.458001532</v>
       </c>
       <c r="K33">
         <f>('Cost Components'!$B$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!K30</f>
-        <v>43164297.289759129</v>
+        <v>46160882.671029463</v>
       </c>
       <c r="L33">
         <f>('Cost Components'!$B$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!L30</f>
-        <v>40340464.756784238</v>
+        <v>43141011.842083611</v>
       </c>
       <c r="M33">
         <f>('Cost Components'!$B$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!M30</f>
-        <v>37701368.931574047</v>
+        <v>40318702.656152904</v>
       </c>
       <c r="N33">
         <f>('Cost Components'!$B$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!N30</f>
-        <v>35234924.235115938</v>
+        <v>37681030.519769073</v>
       </c>
       <c r="O33">
         <f>('Cost Components'!$B$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!O30</f>
-        <v>32929835.733753212</v>
+        <v>35215916.373615958</v>
       </c>
       <c r="P33">
         <f>('Cost Components'!$B$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!P30</f>
-        <v>30775547.414722633</v>
+        <v>32912071.377211176</v>
       </c>
       <c r="Q33">
         <f>('Cost Components'!$B$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!Q30</f>
-        <v>28762193.845535167</v>
+        <v>30758945.212346889</v>
       </c>
       <c r="R33">
         <f>('Cost Components'!$B$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!R30</f>
-        <v>26880554.995827261</v>
+        <v>28746677.7685485</v>
       </c>
       <c r="S33">
         <f>('Cost Components'!$B$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!S30</f>
-        <v>25122014.014791831</v>
+        <v>26866053.989297662</v>
       </c>
       <c r="T33">
         <f>('Cost Components'!$B$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!T30</f>
-        <v>23478517.770833489</v>
+        <v>25108461.672240805</v>
       </c>
       <c r="U33">
         <f>('Cost Components'!$B$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!U30</f>
-        <v>21942539.972741578</v>
+        <v>23465852.030131593</v>
       </c>
       <c r="V33">
         <f>('Cost Components'!$B$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!V30</f>
-        <v>20507046.703496803</v>
+        <v>21930702.831898686</v>
       </c>
       <c r="W33">
         <f>('Cost Components'!$B$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!W30</f>
-        <v>19165464.208875515</v>
+        <v>20495983.955045499</v>
       </c>
       <c r="X33">
         <f>('Cost Components'!$B$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!X30</f>
-        <v>17911648.793341603</v>
+        <v>19155125.19163131</v>
       </c>
       <c r="Y33">
         <f>('Cost Components'!$B$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!Y30</f>
-        <v>16739858.685365984</v>
+        <v>17901986.160403091</v>
       </c>
       <c r="Z33">
         <f>('Cost Components'!$B$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!Z30</f>
-        <v>15644727.743332693</v>
+        <v>16730828.187292608</v>
       </c>
       <c r="AA33">
         <f>('Cost Components'!$B$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!AA30</f>
-        <v>14621240.88161934</v>
+        <v>15636288.025507109</v>
       </c>
     </row>
     <row r="34" spans="1:27">
@@ -10565,103 +10565,103 @@
       </c>
       <c r="C35">
         <f t="shared" si="0"/>
-        <v>84373328.79345794</v>
+        <v>89522020.382242993</v>
       </c>
       <c r="D35">
         <f t="shared" si="0"/>
-        <v>78853578.311642945</v>
+        <v>83665439.609572887</v>
       </c>
       <c r="E35">
         <f t="shared" si="0"/>
-        <v>73694933.00153546</v>
+        <v>78191999.635114849</v>
       </c>
       <c r="F35">
         <f t="shared" si="0"/>
-        <v>68873769.160313517</v>
+        <v>73076635.173004538</v>
       </c>
       <c r="G35">
         <f t="shared" si="0"/>
-        <v>64368008.561040662</v>
+        <v>68295920.722434133</v>
       </c>
       <c r="H35">
         <f t="shared" si="0"/>
-        <v>60157017.346766979</v>
+        <v>63827963.291994527</v>
       </c>
       <c r="I35">
         <f t="shared" si="0"/>
-        <v>56221511.539034553</v>
+        <v>59652302.142050959</v>
       </c>
       <c r="J35">
         <f t="shared" si="0"/>
-        <v>52543468.728069678</v>
+        <v>55749815.086028934</v>
       </c>
       <c r="K35">
         <f t="shared" si="0"/>
-        <v>49106045.540252022</v>
+        <v>52102630.921522357</v>
       </c>
       <c r="L35">
         <f t="shared" si="0"/>
-        <v>45893500.504908442</v>
+        <v>48694047.590207815</v>
       </c>
       <c r="M35">
         <f t="shared" si="0"/>
-        <v>42891121.967204146</v>
+        <v>45508455.691783004</v>
       </c>
       <c r="N35">
         <f t="shared" si="0"/>
-        <v>40085160.717013225</v>
+        <v>42531267.00166636</v>
       </c>
       <c r="O35">
         <f t="shared" si="0"/>
-        <v>37462767.025246002</v>
+        <v>39748847.665108748</v>
       </c>
       <c r="P35">
         <f t="shared" si="0"/>
-        <v>35011931.799295336</v>
+        <v>37148455.761783876</v>
       </c>
       <c r="Q35">
         <f t="shared" si="0"/>
-        <v>32721431.588126477</v>
+        <v>34718182.954938196</v>
       </c>
       <c r="R35">
         <f t="shared" si="0"/>
-        <v>30580777.185164936</v>
+        <v>32446899.957886174</v>
       </c>
       <c r="S35">
         <f t="shared" si="0"/>
-        <v>28580165.59361209</v>
+        <v>30324205.568117917</v>
       </c>
       <c r="T35">
         <f t="shared" si="0"/>
-        <v>26710435.134216905</v>
+        <v>28340379.035624221</v>
       </c>
       <c r="U35">
         <f t="shared" si="0"/>
-        <v>24963023.489922341</v>
+        <v>26486335.547312357</v>
       </c>
       <c r="V35">
         <f t="shared" si="0"/>
-        <v>23329928.495254524</v>
+        <v>24753584.623656407</v>
       </c>
       <c r="W35">
         <f t="shared" si="0"/>
-        <v>21803671.490892075</v>
+        <v>23134191.237062059</v>
       </c>
       <c r="X35">
         <f t="shared" si="0"/>
-        <v>20377263.075600073</v>
+        <v>21620739.473889779</v>
       </c>
       <c r="Y35">
         <f t="shared" si="0"/>
-        <v>19044171.098691657</v>
+        <v>20206298.573728763</v>
       </c>
       <c r="Z35">
         <f t="shared" si="0"/>
-        <v>17798290.746440798</v>
+        <v>18884391.190400712</v>
       </c>
       <c r="AA35">
         <f t="shared" si="0"/>
-        <v>16633916.58545869</v>
+        <v>17648963.729346458</v>
       </c>
     </row>
     <row r="37" spans="1:27">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="B38" s="26">
         <f>SUM(B31:AA31) /SUM($B$35:$AA$35)</f>
-        <v>0.25634932009095945</v>
+        <v>0.24522127639695937</v>
       </c>
       <c r="C38" s="26"/>
     </row>
@@ -10685,7 +10685,7 @@
       </c>
       <c r="B39" s="26">
         <f>SUM(B32:AA32) /SUM($B$35:$AA$35)</f>
-        <v>-6.5490373036481767E-2</v>
+        <v>-6.2647456455202186E-2</v>
       </c>
       <c r="C39" s="26"/>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="B40" s="26">
         <f>SUM(B33:AA33) /SUM($B$35:$AA$35)</f>
-        <v>0.65367020850851831</v>
+        <v>0.66870427628323936</v>
       </c>
       <c r="C40" s="26"/>
     </row>
@@ -10705,7 +10705,7 @@
       </c>
       <c r="B41" s="26">
         <f>SUM(B34:AA34) /SUM($B$35:$AA$35)</f>
-        <v>0.1554708444370041</v>
+        <v>0.14872190377500352</v>
       </c>
       <c r="C41" s="26"/>
     </row>
@@ -10998,103 +10998,103 @@
       </c>
       <c r="C47">
         <f>('Cost Components'!$H$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!C44</f>
-        <v>52441121.4953271</v>
+        <v>57138971.962616824</v>
       </c>
       <c r="D47">
         <f>('Cost Components'!$H$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!D44</f>
-        <v>49010393.920866452</v>
+        <v>53400908.376277409</v>
       </c>
       <c r="E47">
         <f>('Cost Components'!$H$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!E44</f>
-        <v>45804106.468099482</v>
+        <v>49907391.005866736</v>
       </c>
       <c r="F47">
         <f>('Cost Components'!$H$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!F44</f>
-        <v>42807576.138410732</v>
+        <v>46642421.500810035</v>
       </c>
       <c r="G47">
         <f>('Cost Components'!$H$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!G44</f>
-        <v>40007080.503187597</v>
+        <v>43591048.13159816</v>
       </c>
       <c r="H47">
         <f>('Cost Components'!$H$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!H44</f>
-        <v>37389794.862792149</v>
+        <v>40739297.319250621</v>
       </c>
       <c r="I47">
         <f>('Cost Components'!$H$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!I44</f>
-        <v>34943733.516628176</v>
+        <v>38074109.644159459</v>
       </c>
       <c r="J47">
         <f>('Cost Components'!$H$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!J44</f>
-        <v>32657694.875353437</v>
+        <v>35583280.041270517</v>
       </c>
       <c r="K47">
         <f>('Cost Components'!$H$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!K44</f>
-        <v>30521210.163881712</v>
+        <v>33255401.907729454</v>
       </c>
       <c r="L47">
         <f>('Cost Components'!$H$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!L44</f>
-        <v>28524495.480263285</v>
+        <v>31079814.867036875</v>
       </c>
       <c r="M47">
         <f>('Cost Components'!$H$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!M44</f>
-        <v>26658406.990900263</v>
+        <v>29046555.950501747</v>
       </c>
       <c r="N47">
         <f>('Cost Components'!$H$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!N44</f>
-        <v>24914399.05691614</v>
+        <v>27146313.972431544</v>
       </c>
       <c r="O47">
         <f>('Cost Components'!$H$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!O44</f>
-        <v>23284485.099921621</v>
+        <v>25370386.890122939</v>
       </c>
       <c r="P47">
         <f>('Cost Components'!$H$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!P44</f>
-        <v>21761201.027964134</v>
+        <v>23710641.953385923</v>
       </c>
       <c r="Q47">
         <f>('Cost Components'!$H$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!Q44</f>
-        <v>20337571.054172087</v>
+        <v>22159478.461108338</v>
       </c>
       <c r="R47">
         <f>('Cost Components'!$H$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!R44</f>
-        <v>19007075.7515627</v>
+        <v>20709792.95430686</v>
       </c>
       <c r="S47">
         <f>('Cost Components'!$H$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!S44</f>
-        <v>17763622.197722148</v>
+        <v>19354946.686268095</v>
       </c>
       <c r="T47">
         <f>('Cost Components'!$H$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!T44</f>
-        <v>16601516.072637523</v>
+        <v>18088735.220811304</v>
       </c>
       <c r="U47">
         <f>('Cost Components'!$H$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!U44</f>
-        <v>15515435.581904225</v>
+        <v>16905360.019449815</v>
       </c>
       <c r="V47">
         <f>('Cost Components'!$H$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!V44</f>
-        <v>14500407.0858918</v>
+        <v>15799401.887336276</v>
       </c>
       <c r="W47">
         <f>('Cost Components'!$H$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!W44</f>
-        <v>13551782.323263364</v>
+        <v>14765796.156389043</v>
       </c>
       <c r="X47">
         <f>('Cost Components'!$H$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!X44</f>
-        <v>12665217.1245452</v>
+        <v>13799809.491952376</v>
       </c>
       <c r="Y47">
         <f>('Cost Components'!$H$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!Y44</f>
-        <v>11836651.518266542</v>
+        <v>12897018.216777921</v>
       </c>
       <c r="Z47">
         <f>('Cost Components'!$H$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!Z44</f>
-        <v>11062291.138566861</v>
+        <v>12053288.053063478</v>
       </c>
       <c r="AA47">
         <f>('Cost Components'!$H$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!AA44</f>
-        <v>10338589.849127907</v>
+        <v>11264755.18977895</v>
       </c>
     </row>
     <row r="48" spans="1:27">
@@ -11215,103 +11215,103 @@
       </c>
       <c r="C49">
         <f t="shared" si="1"/>
-        <v>63462031.225389838</v>
+        <v>68159881.692679554</v>
       </c>
       <c r="D49">
         <f t="shared" si="1"/>
-        <v>59310309.556439102</v>
+        <v>63700824.011850059</v>
       </c>
       <c r="E49">
         <f t="shared" si="1"/>
-        <v>55430195.847139344</v>
+        <v>59533480.384906597</v>
       </c>
       <c r="F49">
         <f t="shared" si="1"/>
-        <v>51803921.35246668</v>
+        <v>55638766.714865983</v>
       </c>
       <c r="G49">
         <f t="shared" si="1"/>
-        <v>48414879.768660441</v>
+        <v>51998847.397071004</v>
       </c>
       <c r="H49">
         <f t="shared" si="1"/>
-        <v>45247551.185663968</v>
+        <v>48597053.64212244</v>
       </c>
       <c r="I49">
         <f t="shared" si="1"/>
-        <v>42287431.014639221</v>
+        <v>45417807.142170504</v>
       </c>
       <c r="J49">
         <f t="shared" si="1"/>
-        <v>39520963.565083385</v>
+        <v>42446548.731000468</v>
       </c>
       <c r="K49">
         <f t="shared" si="1"/>
-        <v>36935479.967367649</v>
+        <v>39669671.711215392</v>
       </c>
       <c r="L49">
         <f t="shared" si="1"/>
-        <v>34519140.156418361</v>
+        <v>37074459.543191954</v>
       </c>
       <c r="M49">
         <f t="shared" si="1"/>
-        <v>32260878.650858279</v>
+        <v>34649027.61045976</v>
       </c>
       <c r="N49">
         <f t="shared" si="1"/>
-        <v>30150353.879306812</v>
+        <v>32382268.794822216</v>
       </c>
       <c r="O49">
         <f t="shared" si="1"/>
-        <v>28177900.82178206</v>
+        <v>30263802.611983381</v>
       </c>
       <c r="P49">
         <f t="shared" si="1"/>
-        <v>26334486.749329031</v>
+        <v>28283927.67475082</v>
       </c>
       <c r="Q49">
         <f t="shared" si="1"/>
-        <v>24611669.859186009</v>
+        <v>26433577.266122259</v>
       </c>
       <c r="R49">
         <f t="shared" si="1"/>
-        <v>23001560.616061691</v>
+        <v>24704277.818805851</v>
       </c>
       <c r="S49">
         <f t="shared" si="1"/>
-        <v>21496785.62248756</v>
+        <v>23088110.111033507</v>
       </c>
       <c r="T49">
         <f t="shared" si="1"/>
-        <v>20090453.852792114</v>
+        <v>21577673.000965897</v>
       </c>
       <c r="U49">
         <f t="shared" si="1"/>
-        <v>18776125.096067395</v>
+        <v>20166049.533612989</v>
       </c>
       <c r="V49">
         <f t="shared" si="1"/>
-        <v>17547780.463614389</v>
+        <v>18846775.265058868</v>
       </c>
       <c r="W49">
         <f t="shared" si="1"/>
-        <v>16399794.82580784</v>
+        <v>17613808.65893352</v>
       </c>
       <c r="X49">
         <f t="shared" si="1"/>
-        <v>15326911.052156858</v>
+        <v>16461503.419564035</v>
       </c>
       <c r="Y49">
         <f t="shared" si="1"/>
-        <v>14324215.936595194</v>
+        <v>15384582.635106575</v>
       </c>
       <c r="Z49">
         <f t="shared" si="1"/>
-        <v>13387117.697752519</v>
+        <v>14378114.612249136</v>
       </c>
       <c r="AA49">
         <f t="shared" si="1"/>
-        <v>12511324.951170579</v>
+        <v>13437490.291821621</v>
       </c>
     </row>
     <row r="51" spans="1:27">
@@ -11325,7 +11325,7 @@
       </c>
       <c r="B52" s="26">
         <f>SUM(B45:AA45) /SUM($B$49:$AA$49)</f>
-        <v>0.29133588367569391</v>
+        <v>0.27681429354540693</v>
       </c>
       <c r="C52" s="26"/>
     </row>
@@ -11335,7 +11335,7 @@
       </c>
       <c r="B53" s="26">
         <f>SUM(B46:AA46) /SUM($B$49:$AA$49)</f>
-        <v>-2.5829613024810198E-5</v>
+        <v>-2.454214012982088E-5</v>
       </c>
       <c r="C53" s="26"/>
     </row>
@@ -11345,7 +11345,7 @@
       </c>
       <c r="B54" s="26">
         <f>SUM(B47:AA47) /SUM($B$49:$AA$49)</f>
-        <v>0.58559646304975765</v>
+        <v>0.60625234050710297</v>
       </c>
       <c r="C54" s="26"/>
     </row>
@@ -11355,7 +11355,7 @@
       </c>
       <c r="B55" s="26">
         <f>SUM(B48:AA48) /SUM($B$49:$AA$49)</f>
-        <v>0.12309348288757352</v>
+        <v>0.11695790808761979</v>
       </c>
       <c r="C55" s="26"/>
     </row>
@@ -11483,11 +11483,11 @@
       </c>
       <c r="E3" s="21">
         <f>'MFSP CO2 Price Corrected'!B8</f>
-        <v>3.6717494626837071</v>
+        <v>3.8474512116549016</v>
       </c>
       <c r="F3" s="21">
         <f>'MFSP WACC Corrected'!B8</f>
-        <v>3.8243100954201164</v>
+        <v>4.0000118443913113</v>
       </c>
       <c r="H3" s="20" t="s">
         <v>138</v>
@@ -11505,11 +11505,11 @@
       </c>
       <c r="L3" s="21">
         <f>'MFSP CO2 Price Corrected'!B17</f>
-        <v>2.977243530357339</v>
+        <v>3.1375600941433475</v>
       </c>
       <c r="M3" s="21">
         <f>'MFSP WACC Corrected'!B17</f>
-        <v>3.1140925254267096</v>
+        <v>3.2744090892127193</v>
       </c>
       <c r="O3" s="20" t="s">
         <v>138</v>
@@ -11527,11 +11527,11 @@
       </c>
       <c r="S3" s="21">
         <f>'MFSP CO2 Price Corrected'!B26</f>
-        <v>2.7613166824414148</v>
+        <v>2.9216332462274224</v>
       </c>
       <c r="T3" s="21">
         <f>'MFSP WACC Corrected'!B26</f>
-        <v>2.8624581691846087</v>
+        <v>3.0227747329706167</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -11551,11 +11551,11 @@
       </c>
       <c r="E4" s="21">
         <f>E3/Inputs!$C$6</f>
-        <v>4.0797216252041189</v>
+        <v>4.274945790727668</v>
       </c>
       <c r="F4" s="21">
         <f>F3/Inputs!$C$6</f>
-        <v>4.2492334393556845</v>
+        <v>4.4444576048792346</v>
       </c>
       <c r="H4" s="20" t="s">
         <v>138</v>
@@ -11573,11 +11573,11 @@
       </c>
       <c r="L4" s="21">
         <f>L3/Inputs!$C$6</f>
-        <v>3.30804836706371</v>
+        <v>3.4861778823814973</v>
       </c>
       <c r="M4" s="21">
         <f>M3/Inputs!$C$6</f>
-        <v>3.4601028060296772</v>
+        <v>3.6382323213474659</v>
       </c>
       <c r="O4" s="20" t="s">
         <v>138</v>
@@ -11595,11 +11595,11 @@
       </c>
       <c r="S4" s="21">
         <f>S3/Inputs!$C$6</f>
-        <v>3.0681296471571273</v>
+        <v>3.2462591624749138</v>
       </c>
       <c r="T4" s="21">
         <f>T3/Inputs!$C$6</f>
-        <v>3.1805090768717874</v>
+        <v>3.3586385921895738</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -11633,19 +11633,19 @@
       </c>
       <c r="J5" s="22">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="K5" s="22">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="L5" s="22">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="M5" s="22">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="O5" s="20" t="s">
         <v>140</v>
@@ -11655,19 +11655,19 @@
       </c>
       <c r="Q5" s="22">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="R5" s="22">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="S5" s="22">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="T5" s="22">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -11959,11 +11959,11 @@
       </c>
       <c r="E10" s="21">
         <f>((E4-E5) /E9) * 10 ^ 6</f>
-        <v>1257.2448077838119</v>
+        <v>1332.081820343722</v>
       </c>
       <c r="F10" s="21">
         <f>((F4-F5) /F9) * 10 ^ 6</f>
-        <v>1322.2252764194104</v>
+        <v>1397.0622889793208</v>
       </c>
       <c r="H10" s="20" t="s">
         <v>146</v>
@@ -11973,19 +11973,19 @@
       </c>
       <c r="J10" s="21">
         <f>((J4-J5) /J9) * 10 ^ 6</f>
-        <v>575.52240030037865</v>
+        <v>230.51741014820124</v>
       </c>
       <c r="K10" s="21">
         <f>((K4-K5) /K9) * 10 ^ 6</f>
-        <v>575.54862470232217</v>
+        <v>230.54363455014467</v>
       </c>
       <c r="L10" s="21">
         <f>((L4-L5) /L9) * 10 ^ 6</f>
-        <v>961.43244686666662</v>
+        <v>684.71142524562856</v>
       </c>
       <c r="M10" s="21">
         <f>((M4-M5) /M9) * 10 ^ 6</f>
-        <v>1019.7208248867204</v>
+        <v>742.99980326568289</v>
       </c>
       <c r="O10" s="20" t="s">
         <v>146</v>
@@ -11995,19 +11995,19 @@
       </c>
       <c r="Q10" s="21">
         <f>((Q4-Q5) /Q9) * 10 ^ 6</f>
-        <v>483.55222741294153</v>
+        <v>138.54723726076409</v>
       </c>
       <c r="R10" s="21">
         <f>((R4-R5) /R9) * 10 ^ 6</f>
-        <v>483.578451814885</v>
+        <v>138.57346166270756</v>
       </c>
       <c r="S10" s="21">
         <f>((S4-S5) /S9) * 10 ^ 6</f>
-        <v>869.46227397922939</v>
+        <v>592.74125235819088</v>
       </c>
       <c r="T10" s="21">
         <f>((T4-T5) /T9) * 10 ^ 6</f>
-        <v>912.54167847035569</v>
+        <v>635.82065684931717</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -12097,7 +12097,7 @@
       </c>
       <c r="C15">
         <f>C14*10^-6*Inputs!$C$32</f>
-        <v>0.60037290720000014</v>
+        <v>0.64205246160000007</v>
       </c>
       <c r="H15" s="29" t="s">
         <v>149</v>
@@ -12107,7 +12107,7 @@
       </c>
       <c r="J15">
         <f>J14*10^-6*Inputs!$C$33</f>
-        <v>0.22478860800000003</v>
+        <v>0.24492592080000003</v>
       </c>
       <c r="O15" s="29" t="s">
         <v>149</v>
@@ -12117,7 +12117,7 @@
       </c>
       <c r="Q15">
         <f>Q14*10^-6*Inputs!$C$33</f>
-        <v>0.22478860800000003</v>
+        <v>0.24492592080000003</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -12129,7 +12129,7 @@
       </c>
       <c r="C16" s="8">
         <f>C15+F4</f>
-        <v>4.8496063465556851</v>
+        <v>5.0865100664792351</v>
       </c>
       <c r="H16" s="29" t="s">
         <v>150</v>
@@ -12139,7 +12139,7 @@
       </c>
       <c r="J16" s="8">
         <f>J15+M4</f>
-        <v>3.6848914140296771</v>
+        <v>3.883158242147466</v>
       </c>
       <c r="O16" s="29" t="s">
         <v>150</v>
@@ -12149,7 +12149,7 @@
       </c>
       <c r="Q16" s="8">
         <f>Q15+T4</f>
-        <v>3.4052976848717873</v>
+        <v>3.6035645129895739</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -12161,7 +12161,7 @@
       </c>
       <c r="C17" s="8">
         <f>(C16-F5)/F9*10^6</f>
-        <v>1552.3715530151553</v>
+        <v>1643.185959192087</v>
       </c>
       <c r="H17" s="29" t="s">
         <v>151</v>
@@ -12171,7 +12171,7 @@
       </c>
       <c r="J17" s="8">
         <f>(J16-M5)/M9*10^6</f>
-        <v>1105.8910376526778</v>
+        <v>836.88943092525744</v>
       </c>
       <c r="O17" s="29" t="s">
         <v>151</v>
@@ -12181,7 +12181,7 @@
       </c>
       <c r="Q17" s="8">
         <f>(Q16-T5)/T9*10^6</f>
-        <v>998.71189123631302</v>
+        <v>729.71028450889162</v>
       </c>
     </row>
   </sheetData>

--- a/Sensitivity/Harmonization_SAF/Harmonization Sheets/Moretti_2023_Harmonization.xlsx
+++ b/Sensitivity/Harmonization_SAF/Harmonization Sheets/Moretti_2023_Harmonization.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="94" documentId="13_ncr:1_{AD1138F4-22D8-874F-A515-8FAECA50D6A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C3B01BC-B1DB-40B4-9ADF-70F5F5A1DC85}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="28800" windowHeight="15345" tabRatio="1000" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="9960" tabRatio="1000" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Readme" sheetId="1" r:id="rId1"/>
@@ -886,7 +886,7 @@
         </row>
         <row r="34">
           <cell r="C34">
-            <v>523</v>
+            <v>497</v>
           </cell>
         </row>
       </sheetData>
@@ -1235,7 +1235,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1245,9 +1245,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:D33"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6"/>
   <cols>
-    <col min="3" max="3" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="C33" s="4">
         <f>[1]Inputs!C34</f>
-        <v>523</v>
+        <v>497</v>
       </c>
       <c r="D33" t="s">
         <v>29</v>
@@ -1657,9 +1657,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:F41"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="18.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="2" customFormat="1">
@@ -2215,7 +2215,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:Q38"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.5" bestFit="1" customWidth="1"/>
@@ -3508,7 +3508,7 @@
       </c>
       <c r="H36" s="15">
         <f>(Inputs!$C$33 * 'Study Parameters'!$C$18 * 1000) / 10 ^ 6</f>
-        <v>61.138700000000007</v>
+        <v>58.099299999999999</v>
       </c>
       <c r="I36" s="12" t="s">
         <v>75</v>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="N36" s="15">
         <f>(Inputs!$C$33 * 'Study Parameters'!$C$18 * 1000) / 10 ^ 6</f>
-        <v>61.138700000000007</v>
+        <v>58.099299999999999</v>
       </c>
       <c r="O36" s="12" t="s">
         <v>75</v>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="H37" s="18">
         <f>H35-H28+H36</f>
-        <v>74.752691399539572</v>
+        <v>71.713291399539557</v>
       </c>
       <c r="I37" s="17" t="s">
         <v>75</v>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="N37" s="18">
         <f>N35-N28+N36</f>
-        <v>72.612041399539578</v>
+        <v>69.572641399539563</v>
       </c>
       <c r="O37" s="17" t="s">
         <v>75</v>
@@ -3621,10 +3621,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:AA27"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="26.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.8984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.09765625" bestFit="1" customWidth="1"/>
     <col min="3" max="27" width="15.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5232,9 +5232,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:AA26"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="26.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.8984375" bestFit="1" customWidth="1"/>
     <col min="2" max="27" width="15.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6843,9 +6843,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:AA26"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="26.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.8984375" bestFit="1" customWidth="1"/>
     <col min="2" max="27" width="15.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7479,103 +7479,103 @@
       </c>
       <c r="C12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>74752691.399539575</v>
+        <v>71713291.39953956</v>
       </c>
       <c r="D12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>74752691.399539575</v>
+        <v>71713291.39953956</v>
       </c>
       <c r="E12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>74752691.399539575</v>
+        <v>71713291.39953956</v>
       </c>
       <c r="F12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>74752691.399539575</v>
+        <v>71713291.39953956</v>
       </c>
       <c r="G12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>74752691.399539575</v>
+        <v>71713291.39953956</v>
       </c>
       <c r="H12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>74752691.399539575</v>
+        <v>71713291.39953956</v>
       </c>
       <c r="I12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>74752691.399539575</v>
+        <v>71713291.39953956</v>
       </c>
       <c r="J12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>74752691.399539575</v>
+        <v>71713291.39953956</v>
       </c>
       <c r="K12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>74752691.399539575</v>
+        <v>71713291.39953956</v>
       </c>
       <c r="L12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>74752691.399539575</v>
+        <v>71713291.39953956</v>
       </c>
       <c r="M12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>74752691.399539575</v>
+        <v>71713291.39953956</v>
       </c>
       <c r="N12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>74752691.399539575</v>
+        <v>71713291.39953956</v>
       </c>
       <c r="O12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>74752691.399539575</v>
+        <v>71713291.39953956</v>
       </c>
       <c r="P12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>74752691.399539575</v>
+        <v>71713291.39953956</v>
       </c>
       <c r="Q12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>74752691.399539575</v>
+        <v>71713291.39953956</v>
       </c>
       <c r="R12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>74752691.399539575</v>
+        <v>71713291.39953956</v>
       </c>
       <c r="S12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>74752691.399539575</v>
+        <v>71713291.39953956</v>
       </c>
       <c r="T12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>74752691.399539575</v>
+        <v>71713291.39953956</v>
       </c>
       <c r="U12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>74752691.399539575</v>
+        <v>71713291.39953956</v>
       </c>
       <c r="V12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>74752691.399539575</v>
+        <v>71713291.39953956</v>
       </c>
       <c r="W12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>74752691.399539575</v>
+        <v>71713291.39953956</v>
       </c>
       <c r="X12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>74752691.399539575</v>
+        <v>71713291.39953956</v>
       </c>
       <c r="Y12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>74752691.399539575</v>
+        <v>71713291.39953956</v>
       </c>
       <c r="Z12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>74752691.399539575</v>
+        <v>71713291.39953956</v>
       </c>
       <c r="AA12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>74752691.399539575</v>
+        <v>71713291.39953956</v>
       </c>
     </row>
     <row r="13" spans="1:27">
@@ -7588,103 +7588,103 @@
       </c>
       <c r="C13" s="8">
         <f>C12 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!C11</f>
-        <v>71035183.46487765</v>
+        <v>68146935.127848804</v>
       </c>
       <c r="D13" s="8">
         <f>D12 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!D11</f>
-        <v>67502550.01413776</v>
+        <v>64757936.453451507</v>
       </c>
       <c r="E13" s="8">
         <f>E12 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!E11</f>
-        <v>64145597.099275671</v>
+        <v>61537475.248766087</v>
       </c>
       <c r="F13" s="8">
         <f>F12 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!F11</f>
-        <v>60955587.994243585</v>
+        <v>58477170.017832823</v>
       </c>
       <c r="G13" s="8">
         <f>G12 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!G11</f>
-        <v>57924220.456994221</v>
+        <v>55569056.082831316</v>
       </c>
       <c r="H13" s="8">
         <f>H12 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!H11</f>
-        <v>55043605.122262478</v>
+        <v>52805564.855398782</v>
       </c>
       <c r="I13" s="8">
         <f>I12 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!I11</f>
-        <v>52306244.968890548</v>
+        <v>50179504.138801508</v>
       </c>
       <c r="J13" s="8">
         <f>J12 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!J11</f>
-        <v>49705015.808258347</v>
+        <v>47684039.409694165</v>
       </c>
       <c r="K13" s="8">
         <f>K12 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!K11</f>
-        <v>47233147.743039295</v>
+        <v>45312676.030751504</v>
       </c>
       <c r="L13" s="8">
         <f>L12 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!L11</f>
-        <v>44884207.548025928</v>
+        <v>43059242.347879156</v>
       </c>
       <c r="M13" s="8">
         <f>M12 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!M11</f>
-        <v>42652081.927170672</v>
+        <v>40917873.628013141</v>
       </c>
       <c r="N13" s="8">
         <f>N12 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!N11</f>
-        <v>40530961.603266388</v>
+        <v>38882996.795704588</v>
       </c>
       <c r="O13" s="8">
         <f>O12 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!O11</f>
-        <v>38515326.198859416</v>
+        <v>36949315.928765848</v>
       </c>
       <c r="P13" s="8">
         <f>P12 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!P11</f>
-        <v>36599929.869046003</v>
+        <v>35111798.475228868</v>
       </c>
       <c r="Q13" s="8">
         <f>Q12 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!Q11</f>
-        <v>34779787.648760855</v>
+        <v>33365662.155744888</v>
       </c>
       <c r="R13" s="8">
         <f>R12 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!R11</f>
-        <v>33050162.479025196</v>
+        <v>31706362.517337549</v>
       </c>
       <c r="S13" s="8">
         <f>S12 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!S11</f>
-        <v>31406552.878389478</v>
+        <v>30129581.106117405</v>
       </c>
       <c r="T13" s="8">
         <f>T12 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!T11</f>
-        <v>29844681.227484457</v>
+        <v>28631214.228176184</v>
       </c>
       <c r="U13" s="8">
         <f>U12 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!U11</f>
-        <v>28360482.636190489</v>
+        <v>27207362.269410376</v>
       </c>
       <c r="V13" s="8">
         <f>V12 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!V11</f>
-        <v>26950094.364450887</v>
+        <v>25854319.546478022</v>
       </c>
       <c r="W13" s="8">
         <f>W12 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!W11</f>
-        <v>25609845.769196283</v>
+        <v>24568564.662475154</v>
       </c>
       <c r="X13" s="8">
         <f>X12 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!X11</f>
-        <v>24336248.751215979</v>
+        <v>23346751.342231695</v>
       </c>
       <c r="Y13" s="8">
         <f>Y12 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!Y11</f>
-        <v>23125988.677113701</v>
+        <v>22185699.723375071</v>
       </c>
       <c r="Z13" s="8">
         <f>Z12 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!Z11</f>
-        <v>21975915.75272128</v>
+        <v>21082388.080495786</v>
       </c>
       <c r="AA13" s="8">
         <f>AA12 / (1+'Study Parameters'!$C$12) ^'MFSP Baseline'!AA11</f>
-        <v>20883036.825519115</v>
+        <v>20033944.96087658</v>
       </c>
     </row>
     <row r="14" spans="1:27">
@@ -7910,7 +7910,7 @@
       </c>
       <c r="B17" s="8">
         <f>SUM(B13:AA13) / SUM(B15:AA15)</f>
-        <v>3.1375600941433475</v>
+        <v>3.0406244974355281</v>
       </c>
     </row>
     <row r="19" spans="1:27">
@@ -8011,103 +8011,103 @@
       </c>
       <c r="C21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>72612041.399539575</v>
+        <v>69572641.39953956</v>
       </c>
       <c r="D21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>72612041.399539575</v>
+        <v>69572641.39953956</v>
       </c>
       <c r="E21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>72612041.399539575</v>
+        <v>69572641.39953956</v>
       </c>
       <c r="F21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>72612041.399539575</v>
+        <v>69572641.39953956</v>
       </c>
       <c r="G21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>72612041.399539575</v>
+        <v>69572641.39953956</v>
       </c>
       <c r="H21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>72612041.399539575</v>
+        <v>69572641.39953956</v>
       </c>
       <c r="I21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>72612041.399539575</v>
+        <v>69572641.39953956</v>
       </c>
       <c r="J21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>72612041.399539575</v>
+        <v>69572641.39953956</v>
       </c>
       <c r="K21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>72612041.399539575</v>
+        <v>69572641.39953956</v>
       </c>
       <c r="L21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>72612041.399539575</v>
+        <v>69572641.39953956</v>
       </c>
       <c r="M21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>72612041.399539575</v>
+        <v>69572641.39953956</v>
       </c>
       <c r="N21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>72612041.399539575</v>
+        <v>69572641.39953956</v>
       </c>
       <c r="O21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>72612041.399539575</v>
+        <v>69572641.39953956</v>
       </c>
       <c r="P21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>72612041.399539575</v>
+        <v>69572641.39953956</v>
       </c>
       <c r="Q21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>72612041.399539575</v>
+        <v>69572641.39953956</v>
       </c>
       <c r="R21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>72612041.399539575</v>
+        <v>69572641.39953956</v>
       </c>
       <c r="S21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>72612041.399539575</v>
+        <v>69572641.39953956</v>
       </c>
       <c r="T21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>72612041.399539575</v>
+        <v>69572641.39953956</v>
       </c>
       <c r="U21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>72612041.399539575</v>
+        <v>69572641.39953956</v>
       </c>
       <c r="V21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>72612041.399539575</v>
+        <v>69572641.39953956</v>
       </c>
       <c r="W21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>72612041.399539575</v>
+        <v>69572641.39953956</v>
       </c>
       <c r="X21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>72612041.399539575</v>
+        <v>69572641.39953956</v>
       </c>
       <c r="Y21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>72612041.399539575</v>
+        <v>69572641.39953956</v>
       </c>
       <c r="Z21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>72612041.399539575</v>
+        <v>69572641.39953956</v>
       </c>
       <c r="AA21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>72612041.399539575</v>
+        <v>69572641.39953956</v>
       </c>
     </row>
     <row r="22" spans="1:27">
@@ -8120,103 +8120,103 @@
       </c>
       <c r="C22" s="24">
         <f>C21/((1+'Study Parameters'!$C$14) ^'MFSP CO2 Price Corrected'!C20)</f>
-        <v>68918034.737603992</v>
+        <v>66033258.731529571</v>
       </c>
       <c r="D22" s="24">
         <f>D21/((1+'Study Parameters'!$C$14) ^'MFSP CO2 Price Corrected'!D20)</f>
-        <v>65411954.003040999</v>
+        <v>62673935.774040975</v>
       </c>
       <c r="E22" s="24">
         <f>E21/((1+'Study Parameters'!$C$14) ^'MFSP CO2 Price Corrected'!E20)</f>
-        <v>62084238.803190008</v>
+        <v>59485512.314010032</v>
       </c>
       <c r="F22" s="24">
         <f>F21/((1+'Study Parameters'!$C$14) ^'MFSP CO2 Price Corrected'!F20)</f>
-        <v>58925815.113126427</v>
+        <v>56459294.147693641</v>
       </c>
       <c r="G22" s="24">
         <f>G21/((1+'Study Parameters'!$C$14) ^'MFSP CO2 Price Corrected'!G20)</f>
-        <v>55928070.532580122</v>
+        <v>53587029.373285532</v>
       </c>
       <c r="H22" s="24">
         <f>H21/((1+'Study Parameters'!$C$14) ^'MFSP CO2 Price Corrected'!H20)</f>
-        <v>53082830.801613629</v>
+        <v>50860885.889602818</v>
       </c>
       <c r="I22" s="24">
         <f>I21/((1+'Study Parameters'!$C$14) ^'MFSP CO2 Price Corrected'!I20)</f>
-        <v>50382337.511022806</v>
+        <v>48273430.039486349</v>
       </c>
       <c r="J22" s="24">
         <f>J21/((1+'Study Parameters'!$C$14) ^'MFSP CO2 Price Corrected'!J20)</f>
-        <v>47819226.946680717</v>
+        <v>45817606.339679524</v>
       </c>
       <c r="K22" s="24">
         <f>K21/((1+'Study Parameters'!$C$14) ^'MFSP CO2 Price Corrected'!K20)</f>
-        <v>45386510.010137349</v>
+        <v>43486718.241912983</v>
       </c>
       <c r="L22" s="24">
         <f>L21/((1+'Study Parameters'!$C$14) ^'MFSP CO2 Price Corrected'!L20)</f>
-        <v>43077553.160722613</v>
+        <v>41274409.87273442</v>
       </c>
       <c r="M22" s="24">
         <f>M21/((1+'Study Parameters'!$C$14) ^'MFSP CO2 Price Corrected'!M20)</f>
-        <v>40886060.327185467</v>
+        <v>39174648.702291586</v>
       </c>
       <c r="N22" s="24">
         <f>N21/((1+'Study Parameters'!$C$14) ^'MFSP CO2 Price Corrected'!N20)</f>
-        <v>38806055.739545815</v>
+        <v>37181709.094809778</v>
       </c>
       <c r="O22" s="24">
         <f>O21/((1+'Study Parameters'!$C$14) ^'MFSP CO2 Price Corrected'!O20)</f>
-        <v>36831867.634344921</v>
+        <v>35290156.695909046</v>
       </c>
       <c r="P22" s="24">
         <f>P21/((1+'Study Parameters'!$C$14) ^'MFSP CO2 Price Corrected'!P20)</f>
-        <v>34958112.788861923</v>
+        <v>33494833.614188541</v>
       </c>
       <c r="Q22" s="24">
         <f>Q21/((1+'Study Parameters'!$C$14) ^'MFSP CO2 Price Corrected'!Q20)</f>
-        <v>33179681.842124067</v>
+        <v>31790844.356670976</v>
       </c>
       <c r="R22" s="24">
         <f>R21/((1+'Study Parameters'!$C$14) ^'MFSP CO2 Price Corrected'!R20)</f>
-        <v>31491725.36268419</v>
+        <v>30173542.47975605</v>
       </c>
       <c r="S22" s="24">
         <f>S21/((1+'Study Parameters'!$C$14) ^'MFSP CO2 Price Corrected'!S20)</f>
-        <v>29889640.625174817</v>
+        <v>28638517.919282503</v>
       </c>
       <c r="T22" s="24">
         <f>T21/((1+'Study Parameters'!$C$14) ^'MFSP CO2 Price Corrected'!T20)</f>
-        <v>28369059.059581261</v>
+        <v>27181584.965150438</v>
       </c>
       <c r="U22" s="24">
         <f>U21/((1+'Study Parameters'!$C$14) ^'MFSP CO2 Price Corrected'!U20)</f>
-        <v>26925834.339010309</v>
+        <v>25798770.84771302</v>
       </c>
       <c r="V22" s="24">
         <f>V21/((1+'Study Parameters'!$C$14) ^'MFSP CO2 Price Corrected'!V20)</f>
-        <v>25556031.073472198</v>
+        <v>24486304.904814936</v>
       </c>
       <c r="W22" s="24">
         <f>W21/((1+'Study Parameters'!$C$14) ^'MFSP CO2 Price Corrected'!W20)</f>
-        <v>24255914.078846045</v>
+        <v>23240608.299938243</v>
       </c>
       <c r="X22" s="24">
         <f>X21/((1+'Study Parameters'!$C$14) ^'MFSP CO2 Price Corrected'!X20)</f>
-        <v>23021938.191767313</v>
+        <v>22058284.263418984</v>
       </c>
       <c r="Y22" s="24">
         <f>Y21/((1+'Study Parameters'!$C$14) ^'MFSP CO2 Price Corrected'!Y20)</f>
-        <v>21850738.602664497</v>
+        <v>20936108.830124319</v>
       </c>
       <c r="Z22" s="24">
         <f>Z21/((1+'Study Parameters'!$C$14) ^'MFSP CO2 Price Corrected'!Z20)</f>
-        <v>20739121.680585131</v>
+        <v>19871022.048333634</v>
       </c>
       <c r="AA22" s="24">
         <f>AA21/((1+'Study Parameters'!$C$14) ^'MFSP CO2 Price Corrected'!AA20)</f>
-        <v>19684056.264792267</v>
+        <v>18860119.635851968</v>
       </c>
     </row>
     <row r="23" spans="1:27">
@@ -8442,7 +8442,7 @@
       </c>
       <c r="B26" s="8">
         <f>SUM(B22:AA22) / SUM(B24:AA24)</f>
-        <v>2.9216332462274224</v>
+        <v>2.824697649519603</v>
       </c>
     </row>
   </sheetData>
@@ -8454,9 +8454,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:AD55"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="26.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.8984375" bestFit="1" customWidth="1"/>
     <col min="2" max="27" width="15.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9090,103 +9090,103 @@
       </c>
       <c r="C12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>74752691.399539575</v>
+        <v>71713291.39953956</v>
       </c>
       <c r="D12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>74752691.399539575</v>
+        <v>71713291.39953956</v>
       </c>
       <c r="E12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>74752691.399539575</v>
+        <v>71713291.39953956</v>
       </c>
       <c r="F12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>74752691.399539575</v>
+        <v>71713291.39953956</v>
       </c>
       <c r="G12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>74752691.399539575</v>
+        <v>71713291.39953956</v>
       </c>
       <c r="H12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>74752691.399539575</v>
+        <v>71713291.39953956</v>
       </c>
       <c r="I12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>74752691.399539575</v>
+        <v>71713291.39953956</v>
       </c>
       <c r="J12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>74752691.399539575</v>
+        <v>71713291.39953956</v>
       </c>
       <c r="K12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>74752691.399539575</v>
+        <v>71713291.39953956</v>
       </c>
       <c r="L12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>74752691.399539575</v>
+        <v>71713291.39953956</v>
       </c>
       <c r="M12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>74752691.399539575</v>
+        <v>71713291.39953956</v>
       </c>
       <c r="N12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>74752691.399539575</v>
+        <v>71713291.39953956</v>
       </c>
       <c r="O12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>74752691.399539575</v>
+        <v>71713291.39953956</v>
       </c>
       <c r="P12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>74752691.399539575</v>
+        <v>71713291.39953956</v>
       </c>
       <c r="Q12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>74752691.399539575</v>
+        <v>71713291.39953956</v>
       </c>
       <c r="R12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>74752691.399539575</v>
+        <v>71713291.39953956</v>
       </c>
       <c r="S12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>74752691.399539575</v>
+        <v>71713291.39953956</v>
       </c>
       <c r="T12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>74752691.399539575</v>
+        <v>71713291.39953956</v>
       </c>
       <c r="U12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>74752691.399539575</v>
+        <v>71713291.39953956</v>
       </c>
       <c r="V12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>74752691.399539575</v>
+        <v>71713291.39953956</v>
       </c>
       <c r="W12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>74752691.399539575</v>
+        <v>71713291.39953956</v>
       </c>
       <c r="X12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>74752691.399539575</v>
+        <v>71713291.39953956</v>
       </c>
       <c r="Y12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>74752691.399539575</v>
+        <v>71713291.39953956</v>
       </c>
       <c r="Z12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>74752691.399539575</v>
+        <v>71713291.39953956</v>
       </c>
       <c r="AA12" s="11">
         <f>'Cost Components'!$H$37 * 10 ^ 6</f>
-        <v>74752691.399539575</v>
+        <v>71713291.39953956</v>
       </c>
     </row>
     <row r="13" spans="1:27">
@@ -9199,103 +9199,103 @@
       </c>
       <c r="C13" s="8">
         <f>C12 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!C11</f>
-        <v>69862328.410784647</v>
+        <v>67021767.663121082</v>
       </c>
       <c r="D13" s="8">
         <f>D12 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!D11</f>
-        <v>65291895.71101369</v>
+        <v>62637166.040300079</v>
       </c>
       <c r="E13" s="8">
         <f>E12 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!E11</f>
-        <v>61020463.281321205</v>
+        <v>58539407.514299132</v>
       </c>
       <c r="F13" s="8">
         <f>F12 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!F11</f>
-        <v>57028470.356374957</v>
+        <v>54709726.648877703</v>
       </c>
       <c r="G13" s="8">
         <f>G12 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!G11</f>
-        <v>53297635.847079396</v>
+        <v>51130585.65315672</v>
       </c>
       <c r="H13" s="8">
         <f>H12 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!H11</f>
-        <v>49810874.623438694</v>
+        <v>47785594.068370774</v>
       </c>
       <c r="I13" s="8">
         <f>I12 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!I11</f>
-        <v>46552219.274241768</v>
+        <v>44659433.708757728</v>
       </c>
       <c r="J13" s="8">
         <f>J12 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!J11</f>
-        <v>43506746.985272676</v>
+        <v>41737788.51285769</v>
       </c>
       <c r="K13" s="8">
         <f>K12 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!K11</f>
-        <v>40660511.201189414</v>
+        <v>39007278.983979143</v>
       </c>
       <c r="L13" s="8">
         <f>L12 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!L11</f>
-        <v>38000477.758120947</v>
+        <v>36455400.919606678</v>
       </c>
       <c r="M13" s="8">
         <f>M12 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!M11</f>
-        <v>35514465.194505557</v>
+        <v>34070468.149165116</v>
       </c>
       <c r="N13" s="8">
         <f>N12 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!N11</f>
-        <v>33191088.966827627</v>
+        <v>31841559.01791133</v>
       </c>
       <c r="O13" s="8">
         <f>O12 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!O11</f>
-        <v>31019709.314792175</v>
+        <v>29758466.371879745</v>
       </c>
       <c r="P13" s="8">
         <f>P12 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!P11</f>
-        <v>28990382.537188951</v>
+        <v>27811650.814840887</v>
       </c>
       <c r="Q13" s="8">
         <f>Q12 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!Q11</f>
-        <v>27093815.455316771</v>
+        <v>25992197.023215778</v>
       </c>
       <c r="R13" s="8">
         <f>R12 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!R11</f>
-        <v>25321322.855436239</v>
+        <v>24291772.918893255</v>
       </c>
       <c r="S13" s="8">
         <f>S12 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!S11</f>
-        <v>23664787.715360969</v>
+        <v>22702591.51298435</v>
       </c>
       <c r="T13" s="8">
         <f>T12 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!T11</f>
-        <v>22116624.033047635</v>
+        <v>21217375.245779764</v>
       </c>
       <c r="U13" s="8">
         <f>U12 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!U11</f>
-        <v>20669742.086960405</v>
+        <v>19829322.659607258</v>
       </c>
       <c r="V13" s="8">
         <f>V12 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!V11</f>
-        <v>19317515.969121877</v>
+        <v>18532077.251969401</v>
       </c>
       <c r="W13" s="8">
         <f>W12 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!W11</f>
-        <v>18053753.242169976</v>
+        <v>17319698.366326541</v>
       </c>
       <c r="X13" s="8">
         <f>X12 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!X11</f>
-        <v>16872666.581467267</v>
+        <v>16186633.987221066</v>
       </c>
       <c r="Y13" s="8">
         <f>Y12 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!Y11</f>
-        <v>15768847.272399316</v>
+        <v>15127695.315159874</v>
       </c>
       <c r="Z13" s="8">
         <f>Z12 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!Z11</f>
-        <v>14737240.441494687</v>
+        <v>14138033.004822312</v>
       </c>
       <c r="AA13" s="8">
         <f>AA12 / (1+'Cost Components'!$B$38) ^'MFSP Baseline'!AA11</f>
-        <v>13773121.907938959</v>
+        <v>13213114.957777862</v>
       </c>
     </row>
     <row r="14" spans="1:27">
@@ -9521,7 +9521,7 @@
       </c>
       <c r="B17" s="8">
         <f>SUM(B13:AA13) / SUM(B15:AA15)</f>
-        <v>3.2744090892127193</v>
+        <v>3.1774734925048995</v>
       </c>
     </row>
     <row r="19" spans="1:30">
@@ -9622,103 +9622,103 @@
       </c>
       <c r="C21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>72612041.399539575</v>
+        <v>69572641.39953956</v>
       </c>
       <c r="D21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>72612041.399539575</v>
+        <v>69572641.39953956</v>
       </c>
       <c r="E21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>72612041.399539575</v>
+        <v>69572641.39953956</v>
       </c>
       <c r="F21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>72612041.399539575</v>
+        <v>69572641.39953956</v>
       </c>
       <c r="G21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>72612041.399539575</v>
+        <v>69572641.39953956</v>
       </c>
       <c r="H21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>72612041.399539575</v>
+        <v>69572641.39953956</v>
       </c>
       <c r="I21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>72612041.399539575</v>
+        <v>69572641.39953956</v>
       </c>
       <c r="J21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>72612041.399539575</v>
+        <v>69572641.39953956</v>
       </c>
       <c r="K21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>72612041.399539575</v>
+        <v>69572641.39953956</v>
       </c>
       <c r="L21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>72612041.399539575</v>
+        <v>69572641.39953956</v>
       </c>
       <c r="M21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>72612041.399539575</v>
+        <v>69572641.39953956</v>
       </c>
       <c r="N21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>72612041.399539575</v>
+        <v>69572641.39953956</v>
       </c>
       <c r="O21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>72612041.399539575</v>
+        <v>69572641.39953956</v>
       </c>
       <c r="P21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>72612041.399539575</v>
+        <v>69572641.39953956</v>
       </c>
       <c r="Q21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>72612041.399539575</v>
+        <v>69572641.39953956</v>
       </c>
       <c r="R21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>72612041.399539575</v>
+        <v>69572641.39953956</v>
       </c>
       <c r="S21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>72612041.399539575</v>
+        <v>69572641.39953956</v>
       </c>
       <c r="T21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>72612041.399539575</v>
+        <v>69572641.39953956</v>
       </c>
       <c r="U21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>72612041.399539575</v>
+        <v>69572641.39953956</v>
       </c>
       <c r="V21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>72612041.399539575</v>
+        <v>69572641.39953956</v>
       </c>
       <c r="W21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>72612041.399539575</v>
+        <v>69572641.39953956</v>
       </c>
       <c r="X21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>72612041.399539575</v>
+        <v>69572641.39953956</v>
       </c>
       <c r="Y21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>72612041.399539575</v>
+        <v>69572641.39953956</v>
       </c>
       <c r="Z21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>72612041.399539575</v>
+        <v>69572641.39953956</v>
       </c>
       <c r="AA21" s="24">
         <f>'Cost Components'!$N$37 * 10^6</f>
-        <v>72612041.399539575</v>
+        <v>69572641.39953956</v>
       </c>
     </row>
     <row r="22" spans="1:30">
@@ -9731,103 +9731,103 @@
       </c>
       <c r="C22" s="24">
         <f>C21/((1+Inputs!$C$5) ^ 'MFSP WACC Corrected'!C20)</f>
-        <v>67861720.934149131</v>
+        <v>65021160.186485566</v>
       </c>
       <c r="D22" s="24">
         <f>D21/((1+Inputs!$C$5) ^ 'MFSP WACC Corrected'!D20)</f>
-        <v>63422169.097335637</v>
+        <v>60767439.426622026</v>
       </c>
       <c r="E22" s="24">
         <f>E21/((1+Inputs!$C$5) ^ 'MFSP WACC Corrected'!E20)</f>
-        <v>59273055.231154799</v>
+        <v>56791999.464132734</v>
       </c>
       <c r="F22" s="24">
         <f>F21/((1+Inputs!$C$5) ^ 'MFSP WACC Corrected'!F20)</f>
-        <v>55395378.720705427</v>
+        <v>53076635.013208166</v>
       </c>
       <c r="G22" s="24">
         <f>G21/((1+Inputs!$C$5) ^ 'MFSP WACC Corrected'!G20)</f>
-        <v>51771381.98196768</v>
+        <v>49604331.788045011</v>
       </c>
       <c r="H22" s="24">
         <f>H21/((1+Inputs!$C$5) ^ 'MFSP WACC Corrected'!H20)</f>
-        <v>48384469.142025873</v>
+        <v>46359188.586957954</v>
       </c>
       <c r="I22" s="24">
         <f>I21/((1+Inputs!$C$5) ^ 'MFSP WACC Corrected'!I20)</f>
-        <v>45219130.03927651</v>
+        <v>43326344.473792478</v>
       </c>
       <c r="J22" s="24">
         <f>J21/((1+Inputs!$C$5) ^ 'MFSP WACC Corrected'!J20)</f>
-        <v>42260869.195585527</v>
+        <v>40491910.723170541</v>
       </c>
       <c r="K22" s="24">
         <f>K21/((1+Inputs!$C$5) ^ 'MFSP WACC Corrected'!K20)</f>
-        <v>39496139.435126655</v>
+        <v>37842907.217916392</v>
       </c>
       <c r="L22" s="24">
         <f>L21/((1+Inputs!$C$5) ^ 'MFSP WACC Corrected'!L20)</f>
-        <v>36912279.845912769</v>
+        <v>35367203.007398501</v>
       </c>
       <c r="M22" s="24">
         <f>M21/((1+Inputs!$C$5) ^ 'MFSP WACC Corrected'!M20)</f>
-        <v>34497457.799918465</v>
+        <v>33053460.754578032</v>
       </c>
       <c r="N22" s="24">
         <f>N21/((1+Inputs!$C$5) ^ 'MFSP WACC Corrected'!N20)</f>
-        <v>32240614.766278949</v>
+        <v>30891084.817362651</v>
       </c>
       <c r="O22" s="24">
         <f>O21/((1+Inputs!$C$5) ^ 'MFSP WACC Corrected'!O20)</f>
-        <v>30131415.669419575</v>
+        <v>28870172.72650715</v>
       </c>
       <c r="P22" s="24">
         <f>P21/((1+Inputs!$C$5) ^ 'MFSP WACC Corrected'!P20)</f>
-        <v>28160201.560205214</v>
+        <v>26981469.83785715</v>
       </c>
       <c r="Q22" s="24">
         <f>Q21/((1+Inputs!$C$5) ^ 'MFSP WACC Corrected'!Q20)</f>
-        <v>26317945.383369353</v>
+        <v>25216326.95126836</v>
       </c>
       <c r="R22" s="24">
         <f>R21/((1+Inputs!$C$5) ^ 'MFSP WACC Corrected'!R20)</f>
-        <v>24596210.638662953</v>
+        <v>23566660.702119965</v>
       </c>
       <c r="S22" s="24">
         <f>S21/((1+Inputs!$C$5) ^ 'MFSP WACC Corrected'!S20)</f>
-        <v>22987112.746413972</v>
+        <v>22024916.544037353</v>
       </c>
       <c r="T22" s="24">
         <f>T21/((1+Inputs!$C$5) ^ 'MFSP WACC Corrected'!T20)</f>
-        <v>21483282.940573808</v>
+        <v>20584034.153305937</v>
       </c>
       <c r="U22" s="24">
         <f>U21/((1+Inputs!$C$5) ^ 'MFSP WACC Corrected'!U20)</f>
-        <v>20077834.523900751</v>
+        <v>19237415.096547604</v>
       </c>
       <c r="V22" s="24">
         <f>V21/((1+Inputs!$C$5) ^ 'MFSP WACC Corrected'!V20)</f>
-        <v>18764331.330748368</v>
+        <v>17978892.613595892</v>
       </c>
       <c r="W22" s="24">
         <f>W21/((1+Inputs!$C$5) ^ 'MFSP WACC Corrected'!W20)</f>
-        <v>17536758.253035858</v>
+        <v>16802703.377192423</v>
       </c>
       <c r="X22" s="24">
         <f>X21/((1+Inputs!$C$5) ^ 'MFSP WACC Corrected'!X20)</f>
-        <v>16389493.694426036</v>
+        <v>15703461.100179832</v>
       </c>
       <c r="Y22" s="24">
         <f>Y21/((1+Inputs!$C$5) ^ 'MFSP WACC Corrected'!Y20)</f>
-        <v>15317283.826566387</v>
+        <v>14676131.869326947</v>
       </c>
       <c r="Z22" s="24">
         <f>Z21/((1+Inputs!$C$5) ^ 'MFSP WACC Corrected'!Z20)</f>
-        <v>14315218.529501297</v>
+        <v>13716011.092828922</v>
       </c>
       <c r="AA22" s="24">
         <f>AA21/((1+Inputs!$C$5) ^ 'MFSP WACC Corrected'!AA20)</f>
-        <v>13378708.906075977</v>
+        <v>12818701.955914879</v>
       </c>
     </row>
     <row r="23" spans="1:30">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="B26" s="8">
         <f>SUM(B22:AA22) / SUM(B24:AA24)</f>
-        <v>3.0227747329706167</v>
+        <v>2.9258391362627969</v>
       </c>
     </row>
     <row r="29" spans="1:30">
@@ -10998,103 +10998,103 @@
       </c>
       <c r="C47">
         <f>('Cost Components'!$H$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!C44</f>
-        <v>57138971.962616824</v>
+        <v>54298411.214953266</v>
       </c>
       <c r="D47">
         <f>('Cost Components'!$H$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!D44</f>
-        <v>53400908.376277409</v>
+        <v>50746178.705563806</v>
       </c>
       <c r="E47">
         <f>('Cost Components'!$H$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!E44</f>
-        <v>49907391.005866736</v>
+        <v>47426335.23884467</v>
       </c>
       <c r="F47">
         <f>('Cost Components'!$H$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!F44</f>
-        <v>46642421.500810035</v>
+        <v>44323677.793312781</v>
       </c>
       <c r="G47">
         <f>('Cost Components'!$H$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!G44</f>
-        <v>43591048.13159816</v>
+        <v>41423997.937675491</v>
       </c>
       <c r="H47">
         <f>('Cost Components'!$H$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!H44</f>
-        <v>40739297.319250621</v>
+        <v>38714016.764182709</v>
       </c>
       <c r="I47">
         <f>('Cost Components'!$H$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!I44</f>
-        <v>38074109.644159459</v>
+        <v>36181324.078675427</v>
       </c>
       <c r="J47">
         <f>('Cost Components'!$H$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!J44</f>
-        <v>35583280.041270517</v>
+        <v>33814321.568855539</v>
       </c>
       <c r="K47">
         <f>('Cost Components'!$H$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!K44</f>
-        <v>33255401.907729454</v>
+        <v>31602169.690519191</v>
       </c>
       <c r="L47">
         <f>('Cost Components'!$H$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!L44</f>
-        <v>31079814.867036875</v>
+        <v>29534738.028522611</v>
       </c>
       <c r="M47">
         <f>('Cost Components'!$H$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!M44</f>
-        <v>29046555.950501747</v>
+        <v>27602558.905161314</v>
       </c>
       <c r="N47">
         <f>('Cost Components'!$H$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!N44</f>
-        <v>27146313.972431544</v>
+        <v>25796784.023515251</v>
       </c>
       <c r="O47">
         <f>('Cost Components'!$H$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!O44</f>
-        <v>25370386.890122939</v>
+        <v>24109143.947210513</v>
       </c>
       <c r="P47">
         <f>('Cost Components'!$H$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!P44</f>
-        <v>23710641.953385923</v>
+        <v>22531910.231037863</v>
       </c>
       <c r="Q47">
         <f>('Cost Components'!$H$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!Q44</f>
-        <v>22159478.461108338</v>
+        <v>21057860.029007345</v>
       </c>
       <c r="R47">
         <f>('Cost Components'!$H$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!R44</f>
-        <v>20709792.95430686</v>
+        <v>19680243.017763879</v>
       </c>
       <c r="S47">
         <f>('Cost Components'!$H$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!S44</f>
-        <v>19354946.686268095</v>
+        <v>18392750.483891476</v>
       </c>
       <c r="T47">
         <f>('Cost Components'!$H$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!T44</f>
-        <v>18088735.220811304</v>
+        <v>17189486.433543433</v>
       </c>
       <c r="U47">
         <f>('Cost Components'!$H$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!U44</f>
-        <v>16905360.019449815</v>
+        <v>16064940.592096666</v>
       </c>
       <c r="V47">
         <f>('Cost Components'!$H$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!V44</f>
-        <v>15799401.887336276</v>
+        <v>15013963.170183802</v>
       </c>
       <c r="W47">
         <f>('Cost Components'!$H$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!W44</f>
-        <v>14765796.156389043</v>
+        <v>14031741.280545609</v>
       </c>
       <c r="X47">
         <f>('Cost Components'!$H$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!X44</f>
-        <v>13799809.491952376</v>
+        <v>13113776.897706177</v>
       </c>
       <c r="Y47">
         <f>('Cost Components'!$H$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!Y44</f>
-        <v>12897018.216777921</v>
+        <v>12255866.259538483</v>
       </c>
       <c r="Z47">
         <f>('Cost Components'!$H$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!Z44</f>
-        <v>12053288.053063478</v>
+        <v>11454080.616391104</v>
       </c>
       <c r="AA47">
         <f>('Cost Components'!$H$36 * 10^6) / (1+'Cost Components'!$B$38) ^'MFSP WACC Corrected'!AA44</f>
-        <v>11264755.18977895</v>
+        <v>10704748.239617854</v>
       </c>
     </row>
     <row r="48" spans="1:27">
@@ -11215,103 +11215,103 @@
       </c>
       <c r="C49">
         <f t="shared" si="1"/>
-        <v>68159881.692679554</v>
+        <v>65319320.945016004</v>
       </c>
       <c r="D49">
         <f t="shared" si="1"/>
-        <v>63700824.011850059</v>
+        <v>61046094.341136456</v>
       </c>
       <c r="E49">
         <f t="shared" si="1"/>
-        <v>59533480.384906597</v>
+        <v>57052424.617884532</v>
       </c>
       <c r="F49">
         <f t="shared" si="1"/>
-        <v>55638766.714865983</v>
+        <v>53320023.007368729</v>
       </c>
       <c r="G49">
         <f t="shared" si="1"/>
-        <v>51998847.397071004</v>
+        <v>49831797.203148335</v>
       </c>
       <c r="H49">
         <f t="shared" si="1"/>
-        <v>48597053.64212244</v>
+        <v>46571773.087054528</v>
       </c>
       <c r="I49">
         <f t="shared" si="1"/>
-        <v>45417807.142170504</v>
+        <v>43525021.576686472</v>
       </c>
       <c r="J49">
         <f t="shared" si="1"/>
-        <v>42446548.731000468</v>
+        <v>40677590.25858549</v>
       </c>
       <c r="K49">
         <f t="shared" si="1"/>
-        <v>39669671.711215392</v>
+        <v>38016439.494005129</v>
       </c>
       <c r="L49">
         <f t="shared" si="1"/>
-        <v>37074459.543191954</v>
+        <v>35529382.704677686</v>
       </c>
       <c r="M49">
         <f t="shared" si="1"/>
-        <v>34649027.61045976</v>
+        <v>33205030.56511933</v>
       </c>
       <c r="N49">
         <f t="shared" si="1"/>
-        <v>32382268.794822216</v>
+        <v>31032738.845905922</v>
       </c>
       <c r="O49">
         <f t="shared" si="1"/>
-        <v>30263802.611983381</v>
+        <v>29002559.669070952</v>
       </c>
       <c r="P49">
         <f t="shared" si="1"/>
-        <v>28283927.67475082</v>
+        <v>27105195.952402763</v>
       </c>
       <c r="Q49">
         <f t="shared" si="1"/>
-        <v>26433577.266122259</v>
+        <v>25331958.83402127</v>
       </c>
       <c r="R49">
         <f t="shared" si="1"/>
-        <v>24704277.818805851</v>
+        <v>23674727.882262871</v>
       </c>
       <c r="S49">
         <f t="shared" si="1"/>
-        <v>23088110.111033507</v>
+        <v>22125913.908656888</v>
       </c>
       <c r="T49">
         <f t="shared" si="1"/>
-        <v>21577673.000965897</v>
+        <v>20678424.213698026</v>
       </c>
       <c r="U49">
         <f t="shared" si="1"/>
-        <v>20166049.533612989</v>
+        <v>19325630.106259838</v>
       </c>
       <c r="V49">
         <f t="shared" si="1"/>
-        <v>18846775.265058868</v>
+        <v>18061336.547906391</v>
       </c>
       <c r="W49">
         <f t="shared" si="1"/>
-        <v>17613808.65893352</v>
+        <v>16879753.783090085</v>
       </c>
       <c r="X49">
         <f t="shared" si="1"/>
-        <v>16461503.419564035</v>
+        <v>15775470.825317837</v>
       </c>
       <c r="Y49">
         <f t="shared" si="1"/>
-        <v>15384582.635106575</v>
+        <v>14743430.677867137</v>
       </c>
       <c r="Z49">
         <f t="shared" si="1"/>
-        <v>14378114.612249136</v>
+        <v>13778907.175576761</v>
       </c>
       <c r="AA49">
         <f t="shared" si="1"/>
-        <v>13437490.291821621</v>
+        <v>12877483.341660526</v>
       </c>
     </row>
     <row r="51" spans="1:27">
@@ -11325,7 +11325,7 @@
       </c>
       <c r="B52" s="26">
         <f>SUM(B45:AA45) /SUM($B$49:$AA$49)</f>
-        <v>0.27681429354540693</v>
+        <v>0.28541638363240845</v>
       </c>
       <c r="C52" s="26"/>
     </row>
@@ -11335,7 +11335,7 @@
       </c>
       <c r="B53" s="26">
         <f>SUM(B46:AA46) /SUM($B$49:$AA$49)</f>
-        <v>-2.454214012982088E-5</v>
+        <v>-2.5304794751519109E-5</v>
       </c>
       <c r="C53" s="26"/>
     </row>
@@ -11345,7 +11345,7 @@
       </c>
       <c r="B54" s="26">
         <f>SUM(B47:AA47) /SUM($B$49:$AA$49)</f>
-        <v>0.60625234050710297</v>
+        <v>0.5940165097805794</v>
       </c>
       <c r="C54" s="26"/>
     </row>
@@ -11355,7 +11355,7 @@
       </c>
       <c r="B55" s="26">
         <f>SUM(B48:AA48) /SUM($B$49:$AA$49)</f>
-        <v>0.11695790808761979</v>
+        <v>0.12059241138176387</v>
       </c>
       <c r="C55" s="26"/>
     </row>
@@ -11368,20 +11368,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:T17"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.8984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.09765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.59765625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.09765625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.8984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.09765625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
@@ -11505,11 +11505,11 @@
       </c>
       <c r="L3" s="21">
         <f>'MFSP CO2 Price Corrected'!B17</f>
-        <v>3.1375600941433475</v>
+        <v>3.0406244974355281</v>
       </c>
       <c r="M3" s="21">
         <f>'MFSP WACC Corrected'!B17</f>
-        <v>3.2744090892127193</v>
+        <v>3.1774734925048995</v>
       </c>
       <c r="O3" s="20" t="s">
         <v>138</v>
@@ -11527,11 +11527,11 @@
       </c>
       <c r="S3" s="21">
         <f>'MFSP CO2 Price Corrected'!B26</f>
-        <v>2.9216332462274224</v>
+        <v>2.824697649519603</v>
       </c>
       <c r="T3" s="21">
         <f>'MFSP WACC Corrected'!B26</f>
-        <v>3.0227747329706167</v>
+        <v>2.9258391362627969</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -11573,11 +11573,11 @@
       </c>
       <c r="L4" s="21">
         <f>L3/Inputs!$C$6</f>
-        <v>3.4861778823814973</v>
+        <v>3.3784716638172534</v>
       </c>
       <c r="M4" s="21">
         <f>M3/Inputs!$C$6</f>
-        <v>3.6382323213474659</v>
+        <v>3.5305261027832215</v>
       </c>
       <c r="O4" s="20" t="s">
         <v>138</v>
@@ -11595,11 +11595,11 @@
       </c>
       <c r="S4" s="21">
         <f>S3/Inputs!$C$6</f>
-        <v>3.2462591624749138</v>
+        <v>3.1385529439106699</v>
       </c>
       <c r="T4" s="21">
         <f>T3/Inputs!$C$6</f>
-        <v>3.3586385921895738</v>
+        <v>3.2509323736253299</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -11981,11 +11981,11 @@
       </c>
       <c r="L10" s="21">
         <f>((L4-L5) /L9) * 10 ^ 6</f>
-        <v>684.71142524562856</v>
+        <v>643.4234442733117</v>
       </c>
       <c r="M10" s="21">
         <f>((M4-M5) /M9) * 10 ^ 6</f>
-        <v>742.99980326568289</v>
+        <v>701.7118222933658</v>
       </c>
       <c r="O10" s="20" t="s">
         <v>146</v>
@@ -12003,11 +12003,11 @@
       </c>
       <c r="S10" s="21">
         <f>((S4-S5) /S9) * 10 ^ 6</f>
-        <v>592.74125235819088</v>
+        <v>551.45327138587402</v>
       </c>
       <c r="T10" s="21">
         <f>((T4-T5) /T9) * 10 ^ 6</f>
-        <v>635.82065684931717</v>
+        <v>594.5326758770002</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -12107,7 +12107,7 @@
       </c>
       <c r="J15">
         <f>J14*10^-6*Inputs!$C$33</f>
-        <v>0.24492592080000003</v>
+        <v>0.23274987120000004</v>
       </c>
       <c r="O15" s="29" t="s">
         <v>149</v>
@@ -12117,7 +12117,7 @@
       </c>
       <c r="Q15">
         <f>Q14*10^-6*Inputs!$C$33</f>
-        <v>0.24492592080000003</v>
+        <v>0.23274987120000004</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="J16" s="8">
         <f>J15+M4</f>
-        <v>3.883158242147466</v>
+        <v>3.7632759739832218</v>
       </c>
       <c r="O16" s="29" t="s">
         <v>150</v>
@@ -12149,7 +12149,7 @@
       </c>
       <c r="Q16" s="8">
         <f>Q15+T4</f>
-        <v>3.6035645129895739</v>
+        <v>3.4836822448253302</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -12171,7 +12171,7 @@
       </c>
       <c r="J17" s="8">
         <f>(J16-M5)/M9*10^6</f>
-        <v>836.88943092525744</v>
+        <v>790.93389676145102</v>
       </c>
       <c r="O17" s="29" t="s">
         <v>151</v>
@@ -12181,7 +12181,7 @@
       </c>
       <c r="Q17" s="8">
         <f>(Q16-T5)/T9*10^6</f>
-        <v>729.71028450889162</v>
+        <v>683.75475034508543</v>
       </c>
     </row>
   </sheetData>
